--- a/generated/spreadsheet/verbose/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas-verbose.xlsx
+++ b/generated/spreadsheet/verbose/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N166"/>
+  <dimension ref="A1:N165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -642,12 +642,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>application-sub-type</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>submission-date</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>modules</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -786,21 +786,29 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -844,19 +852,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -900,19 +908,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -922,7 +930,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -956,29 +964,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1012,24 +1020,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1068,29 +1076,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>base64-content</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1150,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>base64-content</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1154,7 +1170,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1198,17 +1214,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1218,7 +1234,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1262,22 +1278,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>file-size</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1306,37 +1322,29 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>file-size</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1346,7 +1354,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1380,19 +1388,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1436,75 +1444,67 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>transactions</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>fee</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>transactions</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1514,21 +1514,13 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1536,23 +1528,31 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1586,21 +1586,29 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1610,7 +1618,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1644,24 +1652,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1671,8 +1679,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1680,63 +1696,47 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1754,21 +1754,29 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1778,7 +1786,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1812,19 +1820,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1834,7 +1842,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1868,19 +1876,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -1924,19 +1932,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -1980,19 +1988,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2002,7 +2010,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2026,29 +2034,21 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>user-role</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -2096,12 +2096,12 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2111,64 +2111,56 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>user-role</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2176,23 +2168,31 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2226,21 +2226,29 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2250,7 +2258,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2284,24 +2292,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2311,72 +2319,64 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2394,21 +2394,29 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2418,7 +2426,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2452,19 +2460,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2474,7 +2482,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2508,19 +2516,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2564,19 +2572,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2620,19 +2628,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2642,77 +2650,61 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>flood-risk-assessment</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Results of any flood risk assessments made for the development site</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>flood-risk-area</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Flood risk area</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>flood-risk-assessment</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Results of any flood risk assessments made for the development site</t>
@@ -2720,12 +2712,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>flood-risk-area</t>
+          <t>data-provided-by</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -2736,17 +2728,17 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2760,12 +2752,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>data-provided-by</t>
+          <t>flood-risk-assessment</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -2776,12 +2768,12 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -2800,12 +2792,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>flood-risk-assessment</t>
+          <t>within-20m-watercourse</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -2816,17 +2808,17 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2840,12 +2832,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>within-20m-watercourse</t>
+          <t>increases-flood-risk</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -2856,7 +2848,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -2880,12 +2872,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>increases-flood-risk</t>
+          <t>surface-water-disposal</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Surface water disposal[]</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2896,12 +2888,12 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -2911,21 +2903,29 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="2" t="n"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Results of any flood risk assessments made for the development site</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>surface-water-disposal</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2936,12 +2936,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -2951,16 +2951,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -2968,12 +2960,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>conflict-person-name</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Conflict person name</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -2984,17 +2976,17 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3000,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>conflict-person-name</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -3024,7 +3016,7 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -3039,21 +3031,29 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity, geological and archaeological conservation</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>bio-geo-arch-con</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>protected-species-impact</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Protected species impact</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3064,31 +3064,23 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Where is there a likelihood of protected and priority species being affected?</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity, geological and archaeological conservation</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>bio-geo-arch-con</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
@@ -3096,12 +3088,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>protected-species-impact</t>
+          <t>biodiversity-features-impact</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Protected species impact</t>
+          <t>Biodiversity features impact</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -3112,7 +3104,7 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of protected and priority species being affected?</t>
+          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -3136,12 +3128,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>biodiversity-features-impact</t>
+          <t>geological-features-impact</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity features impact</t>
+          <t>Geological features impact</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -3152,7 +3144,7 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
+          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -3176,12 +3168,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>geological-features-impact</t>
+          <t>archaeological-features-impact</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Geological features impact</t>
+          <t>Archaeological features impact</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -3192,7 +3184,7 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
+          <t>Where is there a likelihood of features of archaeological conservation importance being affected?</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -3207,21 +3199,29 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n"/>
-      <c r="B54" s="2" t="n"/>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>archaeological-features-impact</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Archaeological features impact</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
@@ -3232,12 +3232,12 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of archaeological conservation importance being affected?</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -3249,27 +3249,27 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Declaration</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>checklist</t>
+          <t>declaration</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
@@ -3280,7 +3280,7 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -3295,16 +3295,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -3312,12 +3304,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3328,12 +3320,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -3352,12 +3344,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -3368,12 +3360,12 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -3383,21 +3375,29 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="2" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Designated areas</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>designated-areas</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any 'designated area' the develpoment site is on, such as a Conservation Area or National Park.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>designations</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Designations[]</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -3408,12 +3408,12 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>List of designated areas that apply to the site</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -3425,43 +3425,51 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Designated areas</t>
+          <t>Employment</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>designated-areas</t>
+          <t>employment</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Details of any 'designated area' the develpoment site is on, such as a Conservation Area or National Park.</t>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>designations</t>
+          <t>existing-employees</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Designations[]</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
+          <t>Existing employees</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>full-time</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>List of designated areas that apply to the site</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -3471,16 +3479,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>employment</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>How the proposed development will impact existing and proposed employee numbers</t>
@@ -3498,12 +3498,12 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>full-time</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -3512,7 +3512,7 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>total-fte</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -3560,7 +3560,7 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -3584,22 +3584,22 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>existing-employees</t>
+          <t>proposed-employees</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>total-fte</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -3608,7 +3608,7 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>full-time</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -3656,7 +3656,7 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>total-fte</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -3704,7 +3704,7 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -3719,45 +3719,45 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n"/>
-      <c r="B65" s="2" t="n"/>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Equipment and method</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>equip-method</t>
+        </is>
+      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
+          <t>How oil and gas will be extracted as part of the proposed development.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>proposed-employees</t>
+          <t>equipment-plan</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>total-fte</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Total FTE</t>
-        </is>
-      </c>
+          <t>Equipment plan</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Details of equipment to be used as part of the application including the maximum height and type of drilling rig to be used</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -3769,43 +3769,51 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Equipment and method</t>
+          <t>Existing use</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>equip-method</t>
+          <t>existing-use</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>How oil and gas will be extracted as part of the proposed development.</t>
+          <t>How the site is currently being used.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>equipment-plan</t>
+          <t>existing-use-details</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Equipment plan</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Details of equipment to be used as part of the application including the maximum height and type of drilling rig to be used</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -3815,16 +3823,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>existing-use</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>How the site is currently being used.</t>
@@ -3842,12 +3842,12 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>use-details</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Use details</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -3856,17 +3856,17 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3890,12 +3890,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>use-details</t>
+          <t>land-part</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
+          <t>Land part</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -3904,7 +3904,7 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3928,36 +3928,28 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>existing-use-details</t>
+          <t>site-vacant</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>land-part</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Land part</t>
-        </is>
-      </c>
+          <t>Site vacant</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -3976,12 +3968,12 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>site-vacant</t>
+          <t>last-use-details</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
@@ -3992,17 +3984,17 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4016,12 +4008,12 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>last-use-details</t>
+          <t>last-use-end-date</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
@@ -4032,12 +4024,12 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4056,12 +4048,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>last-use-end-date</t>
+          <t>is-contaminated-land</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -4072,17 +4064,17 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4096,12 +4088,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>is-contaminated-land</t>
+          <t>is-suspected-contaminated-land</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -4112,7 +4104,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -4136,12 +4128,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>is-suspected-contaminated-land</t>
+          <t>proposed-use-contamination-risk</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -4152,7 +4144,7 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -4176,12 +4168,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>proposed-use-contamination-risk</t>
+          <t>contamination-assessment</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -4192,36 +4184,44 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n"/>
-      <c r="B76" s="2" t="n"/>
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Foul sewage disposal</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>foul-sewage</t>
+        </is>
+      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>How the site is currently being used.</t>
+          <t>How waste water will leave the property as part of the proposed development</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>contamination-assessment</t>
+          <t>has-new-disposal-arrangements</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Has new disposal arrangements</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -4232,31 +4232,23 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Does the proposal include any new foul sewage disposal arrangments</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Foul sewage disposal</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>foul-sewage</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>How waste water will leave the property as part of the proposed development</t>
@@ -4264,12 +4256,12 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>has-new-disposal-arrangements</t>
+          <t>foul-sewage-disposal-types</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Has new disposal arrangements</t>
+          <t>Foul sewage disposal types[]</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -4280,17 +4272,17 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include any new foul sewage disposal arrangments</t>
+          <t>List of ways foul sewage will be disposed of</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4304,12 +4296,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>foul-sewage-disposal-types</t>
+          <t>produce-foul-sewage</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Foul sewage disposal types[]</t>
+          <t>Produce foul sewage</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -4320,17 +4312,17 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>List of ways foul sewage will be disposed of</t>
+          <t>Whether the proposed development will produce any foul sewage</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4344,12 +4336,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>produce-foul-sewage</t>
+          <t>connect-to-drainage-system-oil-gas</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Produce foul sewage</t>
+          <t>Connect to drainage system (oil and gas)</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -4360,12 +4352,12 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposed development will produce any foul sewage</t>
+          <t>Whether the proposal needs to connect to the existing drainage system (oil and gas applications)</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -4384,28 +4376,36 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>connect-to-drainage-system-oil-gas</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Connect to drainage system (oil and gas)</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal needs to connect to the existing drainage system (oil and gas applications)</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -4415,45 +4415,45 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n"/>
-      <c r="B81" s="2" t="n"/>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous substances</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>haz-substances</t>
+        </is>
+      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>How waste water will leave the property as part of the proposed development</t>
+          <t>Details of hazardous substances requiring consent used as part of the development</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>hazardous-sub-consent-req</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Hazardous substance consent required</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Does the proposal involve the use or storage of any substances requiring hazardous substances consent</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -4463,16 +4463,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substances</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>haz-substances</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Details of hazardous substances requiring consent used as part of the development</t>
@@ -4480,12 +4472,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>hazardous-sub-consent-req</t>
+          <t>hazardous-sub-consent-details</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance consent required</t>
+          <t>Hazardous substance consent details</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -4496,71 +4488,79 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the use or storage of any substances requiring hazardous substances consent</t>
+          <t>Details of hazardous substance consent requirements</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n"/>
-      <c r="B83" s="2" t="n"/>
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>hrs-operation</t>
+        </is>
+      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Details of hazardous substances requiring consent used as part of the development</t>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>hazardous-sub-consent-details</t>
+          <t>hours-of-operation</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance consent details</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Details of hazardous substance consent requirements</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Hours of operation</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>hrs-operation</t>
-        </is>
-      </c>
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
@@ -4578,12 +4578,12 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>use-other</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Use other</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -4592,17 +4592,17 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4626,31 +4626,39 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>use-other</t>
+          <t>operational-times</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr"/>
-      <c r="I85" s="2" t="inlineStr"/>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>day-type</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Day type</t>
+        </is>
+      </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Day or type of day</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4684,29 +4692,29 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>day-type</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Day type</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Day or type of day</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4740,29 +4748,37 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>time-ranges</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr"/>
-      <c r="K87" s="2" t="inlineStr"/>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>open-time</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Open time</t>
+        </is>
+      </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4806,17 +4822,17 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>open-time</t>
+          <t>close-time</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Open time</t>
+          <t>Close time</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>Closing time</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -4850,47 +4866,31 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>operational-times</t>
+          <t>hours-not-known</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>time-ranges</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>close-time</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>Close time</t>
-        </is>
-      </c>
+          <t>Hours not known</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4904,36 +4904,28 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>hours-of-operation</t>
+          <t>additional-information</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>hours-not-known</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Hours not known</t>
-        </is>
-      </c>
+          <t>Additional information</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Applicant states they do not know the hours of operation</t>
+          <t>Any additional information (such as hours of use of other machinery within the site-generators, pumps, etc)</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -4943,21 +4935,29 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n"/>
-      <c r="B91" s="2" t="n"/>
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>additional-information</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Additional information</t>
+          <t>Sole owner</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -4968,31 +4968,23 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Any additional information (such as hours of use of other machinery within the site-generators, pumps, etc)</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -5000,12 +4992,12 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>agricultural-tenants</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Agricultural tenants</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
@@ -5016,7 +5008,7 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -5040,33 +5032,49 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>agricultural-tenants</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5100,19 +5108,19 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -5122,7 +5130,7 @@
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5156,19 +5164,19 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -5212,19 +5220,19 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -5268,19 +5276,19 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -5290,7 +5298,7 @@
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5314,34 +5322,26 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>notice-date</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Notice date</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -5360,36 +5360,28 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>notice-date</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>Notice date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -5408,23 +5400,31 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5458,12 +5458,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>newspaper-name</t>
+          <t>publication-date</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Publication date</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -5472,12 +5472,12 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -5496,41 +5496,33 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>publication-date</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5544,12 +5536,12 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>applicant-signature</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
+          <t>Applicant signature</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr"/>
@@ -5560,12 +5552,12 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Digital signature of the applicant</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -5584,12 +5576,12 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>applicant-signature</t>
+          <t>agent-signature</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
+          <t>Agent signature</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
@@ -5600,7 +5592,7 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Digital signature of the agent (if applicable)</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -5624,12 +5616,12 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>agent-signature</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
@@ -5640,7 +5632,7 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -5655,21 +5647,29 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n"/>
-      <c r="B106" s="2" t="n"/>
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Access and rights of way</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>access-rights-of-way</t>
+        </is>
+      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>new-altered-vehicle</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>New or altered vehicle access</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
@@ -5680,31 +5680,23 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>Access and rights of way</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>access-rights-of-way</t>
-        </is>
-      </c>
+      <c r="A107" s="2" t="n"/>
+      <c r="B107" s="2" t="n"/>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
@@ -5712,12 +5704,12 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>new-altered-vehicle</t>
+          <t>new-altered-pedestrian</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>New or altered vehicle access</t>
+          <t>New or altered pedestrian access</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
@@ -5728,7 +5720,7 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
+          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
@@ -5752,12 +5744,12 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>new-altered-pedestrian</t>
+          <t>new-right-of-way</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>New or altered pedestrian access</t>
+          <t>New right of way</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
@@ -5768,7 +5760,7 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
+          <t>Will new public rights of way be provided within or adjacent to the site</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
@@ -5792,12 +5784,12 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>new-right-of-way</t>
+          <t>new-public-road</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>New right of way</t>
+          <t>New public road</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
@@ -5808,7 +5800,7 @@
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>Will new public rights of way be provided within or adjacent to the site</t>
+          <t>Will new public roads be provided within the site</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
@@ -5832,12 +5824,12 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>new-public-road</t>
+          <t>temp-right-of-way</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>New public road</t>
+          <t>Temporary right of way changes</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
@@ -5848,7 +5840,7 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>Will new public roads be provided within the site</t>
+          <t>Are temporary changes to rights of way needed while the site is worked</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -5872,12 +5864,12 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>temp-right-of-way</t>
+          <t>future-new-right-of-way</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Temporary right of way changes</t>
+          <t>Future new right of way</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
@@ -5888,7 +5880,7 @@
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>Are temporary changes to rights of way needed while the site is worked</t>
+          <t>Will new public rights of way be provided after extraction?</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
@@ -5912,28 +5904,36 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>future-new-right-of-way</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Future new right of way</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>Will new public rights of way be provided after extraction?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -5943,11 +5943,19 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n"/>
-      <c r="B113" s="2" t="n"/>
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Plans, drawings and supporting materials</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>plans-drawings-supporting-materials</t>
+        </is>
+      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+          <t>Additional materials and specifications that form part of the planning application</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -5991,16 +5999,8 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Plans, drawings and supporting materials</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>plans-drawings-supporting-materials</t>
-        </is>
-      </c>
+      <c r="A114" s="2" t="n"/>
+      <c r="B114" s="2" t="n"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>Additional materials and specifications that form part of the planning application</t>
@@ -6008,31 +6008,23 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>inspection-address</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Inspection address</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Full postal address where supporting material can be inspected</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
@@ -6047,21 +6039,29 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n"/>
-      <c r="B115" s="2" t="n"/>
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Additional materials and specifications that form part of the planning application</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>inspection-address</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Inspection address</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
@@ -6072,12 +6072,12 @@
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>Full postal address where supporting material can be inspected</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -6087,16 +6087,8 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A116" s="2" t="n"/>
+      <c r="B116" s="2" t="n"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -6104,12 +6096,12 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
@@ -6120,17 +6112,17 @@
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6144,12 +6136,12 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr"/>
@@ -6160,7 +6152,7 @@
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
@@ -6184,12 +6176,12 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
@@ -6200,7 +6192,7 @@
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
@@ -6224,12 +6216,12 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
@@ -6240,7 +6232,7 @@
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
@@ -6255,37 +6247,53 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n"/>
-      <c r="B120" s="2" t="n"/>
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>site-boundary</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="H120" s="2" t="inlineStr"/>
       <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -6295,16 +6303,8 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A121" s="2" t="n"/>
+      <c r="B121" s="2" t="n"/>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -6322,12 +6322,12 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr"/>
@@ -6336,12 +6336,12 @@
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr"/>
@@ -6384,7 +6384,7 @@
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr"/>
@@ -6432,12 +6432,12 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -6466,12 +6466,12 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr"/>
@@ -6480,7 +6480,7 @@
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr"/>
@@ -6528,7 +6528,7 @@
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr"/>
@@ -6576,7 +6576,7 @@
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr"/>
@@ -6624,12 +6624,12 @@
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>uprns</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr"/>
@@ -6672,7 +6672,7 @@
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
@@ -6687,31 +6687,39 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n"/>
-      <c r="B129" s="2" t="n"/>
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Site ownership</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>site-ownership</t>
+        </is>
+      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>site-owner</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Site owner</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>fullname</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Full name</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr"/>
@@ -6720,7 +6728,7 @@
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
@@ -6730,21 +6738,13 @@
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Site ownership</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>site-ownership</t>
-        </is>
-      </c>
+      <c r="A130" s="2" t="n"/>
+      <c r="B130" s="2" t="n"/>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>fullname</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr"/>
@@ -6776,7 +6776,7 @@
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
@@ -6800,31 +6800,23 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>site-owner</t>
+          <t>applicant-interest</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Site owner</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>address-text</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Applicant interest</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr"/>
       <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Description of the applicant's interest in the land</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
@@ -6848,12 +6840,12 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>applicant-interest</t>
+          <t>applicant-interest-adjoining-land</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest</t>
+          <t>Applicant interest adjoining land</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr"/>
@@ -6864,7 +6856,7 @@
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>Description of the applicant's interest in the land</t>
+          <t>Description of the applicant's interest in the adjacent land</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
@@ -6879,21 +6871,29 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n"/>
-      <c r="B133" s="2" t="n"/>
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>applicant-interest-adjoining-land</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest adjoining land</t>
+          <t>Site seen from public area</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
@@ -6904,12 +6904,12 @@
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>Description of the applicant's interest in the adjacent land</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
@@ -6919,16 +6919,8 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A134" s="2" t="n"/>
+      <c r="B134" s="2" t="n"/>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -6936,12 +6928,12 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
@@ -6952,12 +6944,12 @@
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -6976,12 +6968,12 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr"/>
@@ -6992,17 +6984,17 @@
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7016,23 +7008,31 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr"/>
-      <c r="G136" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="H136" s="2" t="inlineStr"/>
       <c r="I136" s="2" t="inlineStr"/>
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>fullname</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr"/>
@@ -7080,7 +7080,7 @@
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr"/>
@@ -7128,7 +7128,7 @@
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
@@ -7143,40 +7143,40 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n"/>
-      <c r="B139" s="2" t="n"/>
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Storage facilities</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>storage-facilities</t>
+        </is>
+      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>For oil and gas extraction developments, how chemicals will be stored</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>storage-facilities-description</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Storage facilities description</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr"/>
       <c r="I139" s="2" t="inlineStr"/>
       <c r="J139" s="2" t="inlineStr"/>
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Details and proposed facilities for the storage of oil, fuel and chemicals and the proposed means of their protection</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
@@ -7193,27 +7193,27 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Storage facilities</t>
+          <t>Trade effluent</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>storage-facilities</t>
+          <t>trade-effluent</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>For oil and gas extraction developments, how chemicals will be stored</t>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>storage-facilities-description</t>
+          <t>is-disposal-required</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Storage facilities description</t>
+          <t>Disposal required</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
@@ -7224,12 +7224,12 @@
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>Details and proposed facilities for the storage of oil, fuel and chemicals and the proposed means of their protection</t>
+          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -7239,16 +7239,8 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>Trade effluent</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>trade-effluent</t>
-        </is>
-      </c>
+      <c r="A141" s="2" t="n"/>
+      <c r="B141" s="2" t="n"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
@@ -7256,12 +7248,12 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>is-disposal-required</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Disposal required</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
@@ -7272,36 +7264,44 @@
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
+          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n"/>
-      <c r="B142" s="2" t="n"/>
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>trees-hedges</t>
+        </is>
+      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>trees-on-site</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Trees on site</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
@@ -7312,31 +7312,23 @@
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
+          <t>Whether trees or hedges are present on the proposed development site</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Trees and hedges information</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>trees-hedges</t>
-        </is>
-      </c>
+      <c r="A143" s="2" t="n"/>
+      <c r="B143" s="2" t="n"/>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>Details of trees and/or hedges that will be affected by the proposed development</t>
@@ -7344,12 +7336,12 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>trees-on-site</t>
+          <t>trees-on-adj-land</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Trees on site</t>
+          <t>Trees on adjacent land</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
@@ -7360,7 +7352,7 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges are present on the proposed development site</t>
+          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
@@ -7375,21 +7367,30 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n"/>
-      <c r="B144" s="2" t="n"/>
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Oil and gas permission types</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>oilgas-permission-type</t>
+        </is>
+      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
+</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>trees-on-adj-land</t>
+          <t>oilgas-permission-types</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Trees on adjacent land</t>
+          <t>Oil and gas permission types[]</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
@@ -7400,12 +7401,12 @@
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
+          <t>List of permission types being applied for</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -7415,16 +7416,8 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>Oil and gas permission types</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>oilgas-permission-type</t>
-        </is>
-      </c>
+      <c r="A145" s="2" t="n"/>
+      <c r="B145" s="2" t="n"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
@@ -7433,28 +7426,36 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>oilgas-permission-types</t>
+          <t>related-permissions</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Oil and gas permission types[]</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr"/>
-      <c r="G145" s="2" t="inlineStr"/>
+          <t>Related permissions[]</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H145" s="2" t="inlineStr"/>
       <c r="I145" s="2" t="inlineStr"/>
       <c r="J145" s="2" t="inlineStr"/>
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>List of permission types being applied for</t>
+          <t>The reference for the related application that permission was received for</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -7484,12 +7485,12 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>oilgas-permission-type</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Oil and gas permission type</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr"/>
@@ -7498,12 +7499,12 @@
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application that permission was received for</t>
+          <t>An oil and gas related permission type</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -7533,12 +7534,12 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>oilgas-permission-type</t>
+          <t>decision-date</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Oil and gas permission type</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr"/>
@@ -7547,12 +7548,12 @@
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>An oil and gas related permission type</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -7582,12 +7583,12 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>decision-date</t>
+          <t>condition-number</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Decision date</t>
+          <t>Condition number</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr"/>
@@ -7596,7 +7597,7 @@
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>Number of any condition being breached</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
@@ -7606,7 +7607,7 @@
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7621,31 +7622,23 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>related-permissions</t>
+          <t>other-details</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Related permissions[]</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>condition-number</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>Condition number</t>
-        </is>
-      </c>
+          <t>Other details</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr"/>
       <c r="I149" s="2" t="inlineStr"/>
       <c r="J149" s="2" t="inlineStr"/>
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>Number of any condition being breached</t>
+          <t>Explanation if other ground is selected</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
@@ -7670,12 +7663,12 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>other-details</t>
+          <t>will-consolidate-permissions</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Other details</t>
+          <t>Will consolidate permissions</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr"/>
@@ -7686,17 +7679,17 @@
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>Explanation if other ground is selected</t>
+          <t>Is the applicant looking to consolidate permissions?</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7711,12 +7704,12 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>will-consolidate-permissions</t>
+          <t>details</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Will consolidate permissions</t>
+          <t>Details</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr"/>
@@ -7727,17 +7720,17 @@
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant looking to consolidate permissions?</t>
+          <t>Details about the consolidation or update of permissions</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7752,23 +7745,31 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>details</t>
+          <t>related-proposals</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr"/>
-      <c r="G152" s="2" t="inlineStr"/>
+          <t>Related proposals[]</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H152" s="2" t="inlineStr"/>
       <c r="I152" s="2" t="inlineStr"/>
       <c r="J152" s="2" t="inlineStr"/>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>Details about the consolidation or update of permissions</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
@@ -7778,7 +7779,7 @@
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7803,12 +7804,12 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>application-type</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Application type</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr"/>
@@ -7817,12 +7818,12 @@
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>The type of planning application</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -7852,12 +7853,12 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>application-type</t>
+          <t>decision-date</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Application type</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr"/>
@@ -7866,12 +7867,12 @@
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>The type of planning application</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -7881,46 +7882,45 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n"/>
-      <c r="B155" s="2" t="n"/>
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Development type</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>dev-type</t>
+        </is>
+      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
-</t>
+          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>related-proposals</t>
+          <t>development-phase</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Related proposals[]</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>decision-date</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>Decision date</t>
-        </is>
-      </c>
+          <t>Development phase</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr"/>
       <c r="I155" s="2" t="inlineStr"/>
       <c r="J155" s="2" t="inlineStr"/>
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>Phases of oil and gas development the application covers</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -7930,16 +7930,8 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>Development type</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>dev-type</t>
-        </is>
-      </c>
+      <c r="A156" s="2" t="n"/>
+      <c r="B156" s="2" t="n"/>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
@@ -7947,12 +7939,12 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>development-phase</t>
+          <t>development-description</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Development phase</t>
+          <t>Development description</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr"/>
@@ -7963,12 +7955,12 @@
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>Phases of oil and gas development the application covers</t>
+          <t>Brief description of the development, including main oils, gases, and machinery</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -7987,12 +7979,12 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>development-description</t>
+          <t>quantity-cubic-metres</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Development description</t>
+          <t>Quantity cubic metres</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr"/>
@@ -8003,12 +7995,12 @@
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>Brief description of the development, including main oils, gases, and machinery</t>
+          <t>Quantity of oil or gas involved in cubic metres</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -8027,12 +8019,12 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>quantity-cubic-metres</t>
+          <t>permission-period-years</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Quantity cubic metres</t>
+          <t>Permission period years</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr"/>
@@ -8043,7 +8035,7 @@
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>Quantity of oil or gas involved in cubic metres</t>
+          <t>Period of permission sought in years</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
@@ -8053,7 +8045,7 @@
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8067,12 +8059,12 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>permission-period-years</t>
+          <t>hydrocarbon-licence-block</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Permission period years</t>
+          <t>Hydrocarbon licence block</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
@@ -8083,17 +8075,17 @@
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>Period of permission sought in years</t>
+          <t>Hydrocarbon licence block where the development is located</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8107,12 +8099,12 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>hydrocarbon-licence-block</t>
+          <t>surface-site-area-hectares</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Hydrocarbon licence block</t>
+          <t>Surface site area hectares</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
@@ -8123,17 +8115,17 @@
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>Hydrocarbon licence block where the development is located</t>
+          <t>Surface site area in hectares</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8147,12 +8139,12 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>surface-site-area-hectares</t>
+          <t>site-hectares-provided-by</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Surface site area hectares</t>
+          <t>Site hectares provided by</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr"/>
@@ -8163,12 +8155,12 @@
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>Surface site area in hectares</t>
+          <t>Who provided the site hectares value (applicant or system)</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -8187,12 +8179,12 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>site-hectares-provided-by</t>
+          <t>environmental-statement</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Site hectares provided by</t>
+          <t>Environmental statement</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
@@ -8203,17 +8195,17 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site hectares value (applicant or system)</t>
+          <t>Is an Environmental Statement attached to the application</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8227,12 +8219,12 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>environmental-statement</t>
+          <t>environmental-statement-reference</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Environmental statement</t>
+          <t>Environmental statement reference</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr"/>
@@ -8243,36 +8235,44 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>Is an Environmental Statement attached to the application</t>
+          <t>Reference to the environmental statement document</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n"/>
-      <c r="B164" s="2" t="n"/>
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Voluntary agreement</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>vol-agreement</t>
+        </is>
+      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
+          <t>Details of any voluntary agreements made as part of an oil and gas extraction application.</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>environmental-statement-reference</t>
+          <t>draft-agreement-included</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Environmental statement reference</t>
+          <t>Draft agreement included</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr"/>
@@ -8283,31 +8283,23 @@
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>Reference to the environmental statement document</t>
+          <t>Has an outline or draft agreement been included? (True / False)</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>Voluntary agreement</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>vol-agreement</t>
-        </is>
-      </c>
+      <c r="A165" s="2" t="n"/>
+      <c r="B165" s="2" t="n"/>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>Details of any voluntary agreements made as part of an oil and gas extraction application.</t>
@@ -8315,12 +8307,12 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>draft-agreement-included</t>
+          <t>agreement-summary</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Draft agreement included</t>
+          <t>Agreement summary</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr"/>
@@ -8331,55 +8323,15 @@
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>Has an outline or draft agreement been included? (True / False)</t>
+          <t>Summary of the agreement</t>
         </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="n"/>
-      <c r="B166" s="2" t="n"/>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Details of any voluntary agreements made as part of an oil and gas extraction application.</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>agreement-summary</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>Agreement summary</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr"/>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr"/>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-      <c r="K166" s="2" t="inlineStr"/>
-      <c r="L166" s="2" t="inlineStr">
-        <is>
-          <t>Summary of the agreement</t>
-        </is>
-      </c>
-      <c r="M166" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N166" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -8387,66 +8339,66 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="A92:A106"/>
-    <mergeCell ref="B51:B54"/>
-    <mergeCell ref="B145:B155"/>
-    <mergeCell ref="A140"/>
-    <mergeCell ref="B165:B166"/>
-    <mergeCell ref="B55"/>
-    <mergeCell ref="B134:B139"/>
-    <mergeCell ref="B107:B113"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A60:A65"/>
-    <mergeCell ref="B130:B133"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="A116:A120"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="A67:A76"/>
-    <mergeCell ref="A145:A155"/>
-    <mergeCell ref="A59"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B42:B47"/>
-    <mergeCell ref="A77:A81"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="B59"/>
-    <mergeCell ref="B66"/>
-    <mergeCell ref="A84:A91"/>
-    <mergeCell ref="B140"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="A141:A142"/>
-    <mergeCell ref="B67:B76"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="A156:A164"/>
-    <mergeCell ref="B60:B65"/>
-    <mergeCell ref="A121:A129"/>
-    <mergeCell ref="A165:A166"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A107:A113"/>
-    <mergeCell ref="A143:A144"/>
-    <mergeCell ref="A66"/>
-    <mergeCell ref="A134:A139"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="B84:B91"/>
-    <mergeCell ref="B92:B106"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="A42:A47"/>
-    <mergeCell ref="B141:B142"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B77:B81"/>
-    <mergeCell ref="B156:B164"/>
-    <mergeCell ref="A55"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B121:B129"/>
-    <mergeCell ref="A130:A133"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="B116:B120"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="B35:B40"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="B65"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="B91:B105"/>
+    <mergeCell ref="A83:A90"/>
+    <mergeCell ref="B139"/>
+    <mergeCell ref="A59:A64"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="B66:B75"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A76:A80"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B59:B64"/>
+    <mergeCell ref="A41:A46"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="A115:A119"/>
+    <mergeCell ref="A120:A128"/>
+    <mergeCell ref="A58"/>
+    <mergeCell ref="A144:A154"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="B54"/>
+    <mergeCell ref="A113:A114"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="B76:B80"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="A106:A112"/>
+    <mergeCell ref="A133:A138"/>
+    <mergeCell ref="A155:A163"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="B23:B30"/>
+    <mergeCell ref="B115:B119"/>
+    <mergeCell ref="B58"/>
+    <mergeCell ref="A91:A105"/>
+    <mergeCell ref="A129:A132"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="A65"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="A54"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="A66:A75"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="B106:B112"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="B155:B163"/>
+    <mergeCell ref="B83:B90"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="A139"/>
+    <mergeCell ref="B144:B154"/>
+    <mergeCell ref="B129:B132"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="B133:B138"/>
+    <mergeCell ref="A23:A30"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="B120:B128"/>
+    <mergeCell ref="B41:B46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas-verbose.xlsx
+++ b/generated/spreadsheet/verbose/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas-verbose.xlsx
@@ -4636,19 +4636,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>day-type</t>
+          <t>schedule-days</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Day type</t>
+          <t>Schedule days[]</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Day or type of day</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas-verbose.xlsx
+++ b/generated/spreadsheet/verbose/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas-verbose.xlsx
@@ -7553,7 +7553,7 @@
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas-verbose.xlsx
+++ b/generated/spreadsheet/verbose/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas-verbose.xlsx
@@ -3365,7 +3365,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>development-description</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas-verbose.xlsx
+++ b/generated/spreadsheet/verbose/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N165"/>
+  <dimension ref="A1:N169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -442,7 +442,7 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -521,37 +521,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>submission-reference</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -560,7 +560,7 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -579,17 +579,17 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -627,27 +627,27 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>specification-profile</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -675,27 +675,27 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -723,27 +723,27 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>submitted-at</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -771,49 +771,41 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>created-at</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -827,17 +819,17 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -852,19 +844,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -883,17 +875,17 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -908,19 +900,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -930,7 +922,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -939,17 +931,17 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -964,29 +956,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -995,17 +987,17 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1020,24 +1012,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1051,17 +1043,17 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1076,37 +1068,29 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>base64-content</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1099,17 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1150,17 +1134,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>base64-content</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1170,7 +1154,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1179,17 +1163,17 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1214,17 +1198,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1234,7 +1218,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1227,17 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1278,22 +1262,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>file-size</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1307,54 +1291,62 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>file-size</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1363,17 +1355,17 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1388,24 +1380,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1419,17 +1411,17 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1444,67 +1436,75 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>transactions</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
+          <t>Submission details</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>fee</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>transactions</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1514,13 +1514,21 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1528,31 +1536,23 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1586,29 +1586,21 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1618,7 +1610,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1652,24 +1644,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1679,16 +1671,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1696,47 +1680,63 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1754,29 +1754,21 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1786,7 +1778,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1820,19 +1812,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1842,7 +1834,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1868,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -1932,19 +1924,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -1988,19 +1980,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2010,7 +2002,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2026,29 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -2096,12 +2096,12 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2111,56 +2111,64 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2168,31 +2176,23 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2226,29 +2226,21 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2258,7 +2250,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2292,24 +2284,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2319,64 +2311,72 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="n"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2394,29 +2394,21 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2426,7 +2418,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2460,19 +2452,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2482,7 +2474,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2516,19 +2508,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2572,19 +2564,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2628,19 +2620,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2650,61 +2642,77 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>flood-risk-assessment</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Results of any flood risk assessments made for the development site</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>flood-risk-area</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="n"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>flood-risk-assessment</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Results of any flood risk assessments made for the development site</t>
@@ -2712,12 +2720,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>data-provided-by</t>
+          <t>flood-risk-area</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Flood risk area</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -2728,17 +2736,17 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2752,12 +2760,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>flood-risk-assessment</t>
+          <t>data-provided-by</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -2768,12 +2776,12 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -2792,12 +2800,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>within-20m-watercourse</t>
+          <t>flood-risk-assessment</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -2808,17 +2816,17 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2832,12 +2840,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>increases-flood-risk</t>
+          <t>within-20m-watercourse</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -2848,7 +2856,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -2872,12 +2880,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>surface-water-disposal</t>
+          <t>increases-flood-risk</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2888,12 +2896,12 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -2903,29 +2911,21 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Results of any flood risk assessments made for the development site</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>surface-water-disposal</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Surface water disposal[]</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2936,12 +2936,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -2951,8 +2951,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -2960,12 +2968,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>conflict-person-name</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -2976,17 +2984,17 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3000,12 +3008,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -3016,7 +3024,7 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -3031,29 +3039,21 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity, geological and archaeological conservation</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>bio-geo-arch-con</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>protected-species-impact</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Protected species impact</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3064,23 +3064,31 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of protected and priority species being affected?</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="2" t="n"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity, geological and archaeological conservation</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>bio-geo-arch-con</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
@@ -3088,12 +3096,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>biodiversity-features-impact</t>
+          <t>protected-species-impact</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity features impact</t>
+          <t>Protected species impact</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -3104,7 +3112,7 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
+          <t>Where is there a likelihood of protected and priority species being affected?</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -3128,12 +3136,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>geological-features-impact</t>
+          <t>biodiversity-features-impact</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Geological features impact</t>
+          <t>Biodiversity features impact</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -3144,7 +3152,7 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
+          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -3168,12 +3176,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>archaeological-features-impact</t>
+          <t>geological-features-impact</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Archaeological features impact</t>
+          <t>Geological features impact</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -3184,7 +3192,7 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of archaeological conservation importance being affected?</t>
+          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -3199,29 +3207,21 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>archaeological-features-impact</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Archaeological features impact</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
@@ -3232,12 +3232,12 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Where is there a likelihood of features of archaeological conservation importance being affected?</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -3249,27 +3249,27 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Declaration</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>declaration</t>
+          <t>checklist</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
@@ -3280,7 +3280,7 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -3295,8 +3295,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n"/>
-      <c r="B56" s="2" t="n"/>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -3304,12 +3312,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3320,12 +3328,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -3344,12 +3352,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -3360,12 +3368,12 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -3375,29 +3383,21 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Designated areas</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>designated-areas</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="n"/>
+      <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Details of any 'designated area' the develpoment site is on, such as a Conservation Area or National Park.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>designations</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Designations[]</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -3408,12 +3408,12 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>List of designated areas that apply to the site</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -3425,51 +3425,43 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Employment</t>
+          <t>Designated areas</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>employment</t>
+          <t>designated-areas</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
+          <t>Details of any 'designated area' the develpoment site is on, such as a Conservation Area or National Park.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>existing-employees</t>
+          <t>designations</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>full-time</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
+          <t>Designations[]</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>List of designated areas that apply to the site</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -3479,8 +3471,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n"/>
-      <c r="B60" s="2" t="n"/>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>How the proposed development will impact existing and proposed employee numbers</t>
@@ -3498,12 +3498,12 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -3512,12 +3512,12 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>total-fte</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -3560,12 +3560,12 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -3584,22 +3584,22 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>proposed-employees</t>
+          <t>existing-employees</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>full-time</t>
+          <t>total-fte</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -3608,12 +3608,12 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -3656,12 +3656,12 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>total-fte</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -3704,12 +3704,12 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3719,45 +3719,45 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Equipment and method</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>equip-method</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>How oil and gas will be extracted as part of the proposed development.</t>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>equipment-plan</t>
+          <t>proposed-employees</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Equipment plan</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
+          <t>Proposed employees</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>total-fte</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Total FTE</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Details of equipment to be used as part of the application including the maximum height and type of drilling rig to be used</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -3769,51 +3769,43 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Existing use</t>
+          <t>Equipment and method</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>existing-use</t>
+          <t>equip-method</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>How the site is currently being used.</t>
+          <t>How oil and gas will be extracted as part of the proposed development.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>existing-use-details</t>
+          <t>equipment-plan</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>use</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
+          <t>Equipment plan</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Details of equipment to be used as part of the application including the maximum height and type of drilling rig to be used</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -3823,8 +3815,16 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>existing-use</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>How the site is currently being used.</t>
@@ -3842,12 +3842,12 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>use-details</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -3856,17 +3856,17 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3890,12 +3890,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>land-part</t>
+          <t>use-details</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Land part</t>
+          <t>Use details</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -3904,7 +3904,7 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3928,28 +3928,36 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>site-vacant</t>
+          <t>existing-use-details</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>land-part</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Land part</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -3968,12 +3976,12 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>last-use-details</t>
+          <t>site-vacant</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
+          <t>Site vacant</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
@@ -3984,17 +3992,17 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4008,12 +4016,12 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>last-use-end-date</t>
+          <t>last-use-details</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
@@ -4024,12 +4032,12 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4048,12 +4056,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>is-contaminated-land</t>
+          <t>last-use-end-date</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -4064,17 +4072,17 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4088,12 +4096,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>is-suspected-contaminated-land</t>
+          <t>is-contaminated-land</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -4104,7 +4112,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -4128,12 +4136,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>proposed-use-contamination-risk</t>
+          <t>is-suspected-contaminated-land</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -4144,7 +4152,7 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -4168,12 +4176,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>contamination-assessment</t>
+          <t>proposed-use-contamination-risk</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -4184,44 +4192,36 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Foul sewage disposal</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>foul-sewage</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>How waste water will leave the property as part of the proposed development</t>
+          <t>How the site is currently being used.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>has-new-disposal-arrangements</t>
+          <t>contamination-assessment</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Has new disposal arrangements</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -4232,23 +4232,31 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include any new foul sewage disposal arrangments</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n"/>
-      <c r="B77" s="2" t="n"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Foul sewage disposal</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>foul-sewage</t>
+        </is>
+      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>How waste water will leave the property as part of the proposed development</t>
@@ -4256,12 +4264,12 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>foul-sewage-disposal-types</t>
+          <t>has-new-disposal-arrangements</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Foul sewage disposal types[]</t>
+          <t>Has new disposal arrangements</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -4272,17 +4280,17 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>List of ways foul sewage will be disposed of</t>
+          <t>Does the proposal include any new foul sewage disposal arrangments</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4296,12 +4304,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>produce-foul-sewage</t>
+          <t>foul-sewage-disposal-types</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Produce foul sewage</t>
+          <t>Foul sewage disposal types[]</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -4312,17 +4320,17 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposed development will produce any foul sewage</t>
+          <t>List of ways foul sewage will be disposed of</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4336,12 +4344,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>connect-to-drainage-system-oil-gas</t>
+          <t>produce-foul-sewage</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Connect to drainage system (oil and gas)</t>
+          <t>Produce foul sewage</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -4352,12 +4360,12 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal needs to connect to the existing drainage system (oil and gas applications)</t>
+          <t>Whether the proposed development will produce any foul sewage</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -4376,36 +4384,28 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>connect-to-drainage-system-oil-gas</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Connect to drainage system (oil and gas)</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Whether the proposal needs to connect to the existing drainage system (oil and gas applications)</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -4415,45 +4415,45 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substances</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>haz-substances</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Details of hazardous substances requiring consent used as part of the development</t>
+          <t>How waste water will leave the property as part of the proposed development</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>hazardous-sub-consent-req</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance consent required</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the use or storage of any substances requiring hazardous substances consent</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -4463,8 +4463,16 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n"/>
-      <c r="B82" s="2" t="n"/>
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous substances</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>haz-substances</t>
+        </is>
+      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Details of hazardous substances requiring consent used as part of the development</t>
@@ -4472,12 +4480,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>hazardous-sub-consent-details</t>
+          <t>hazardous-sub-consent-req</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance consent details</t>
+          <t>Hazardous substance consent required</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -4488,79 +4496,71 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Details of hazardous substance consent requirements</t>
+          <t>Does the proposal involve the use or storage of any substances requiring hazardous substances consent</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Hours of operation</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>hrs-operation</t>
-        </is>
-      </c>
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+          <t>Details of hazardous substances requiring consent used as part of the development</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>hours-of-operation</t>
+          <t>hazardous-sub-consent-details</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>use</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
+          <t>Hazardous substance consent details</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Details of hazardous substance consent requirements</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n"/>
-      <c r="B84" s="2" t="n"/>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>hrs-operation</t>
+        </is>
+      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
@@ -4578,12 +4578,12 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>use-other</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -4592,17 +4592,17 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4626,39 +4626,31 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>operational-times</t>
+          <t>use-other</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>schedule-days</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>Schedule days[]</t>
-        </is>
-      </c>
+          <t>Use other</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>List of days or day categories that a schedule entry applies to</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4692,29 +4684,29 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>schedule-days</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Schedule days[]</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4748,37 +4740,29 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>time-ranges</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>open-time</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>Open time</t>
-        </is>
-      </c>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4822,17 +4806,17 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>close-time</t>
+          <t>open-time</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Close time</t>
+          <t>Open time</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -4866,31 +4850,47 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>hours-not-known</t>
+          <t>operational-times</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Hours not known</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-      <c r="K89" s="2" t="inlineStr"/>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>time-ranges</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>close-time</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Close time</t>
+        </is>
+      </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Applicant states they do not know the hours of operation</t>
+          <t>Closing time</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4904,28 +4904,36 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>additional-information</t>
+          <t>hours-of-operation</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Additional information</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>hours-not-known</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Hours not known</t>
+        </is>
+      </c>
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Any additional information (such as hours of use of other machinery within the site-generators, pumps, etc)</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -4935,29 +4943,21 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>additional-information</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Additional information</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -4968,57 +4968,81 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Any additional information (such as hours of use of other machinery within the site-generators, pumps, etc)</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n"/>
-      <c r="B92" s="2" t="n"/>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Oil and gas ownership and notices</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>oil-gas-ownership-notices</t>
+        </is>
+      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>agricultural-tenants</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5051,7 @@
       <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5052,19 +5076,19 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -5074,7 +5098,7 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5107,7 @@
       <c r="B94" s="2" t="n"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -5108,19 +5132,19 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -5139,7 +5163,7 @@
       <c r="B95" s="2" t="n"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -5164,19 +5188,19 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -5195,7 +5219,7 @@
       <c r="B96" s="2" t="n"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -5220,19 +5244,19 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -5242,7 +5266,7 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5275,7 @@
       <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -5266,34 +5290,26 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>notice-served-date</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Notice served date</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -5307,27 +5323,27 @@
       <c r="B98" s="2" t="n"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>valid-posted-notices</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
+          <t>Valid posted notices[]</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>notice-date</t>
+          <t>parish-ward</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Notice date</t>
+          <t>Parish or ward</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
@@ -5336,17 +5352,17 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Parish or ward where the notice was posted</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5355,28 +5371,36 @@
       <c r="B99" s="2" t="n"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>valid-posted-notices</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="inlineStr"/>
+          <t>Valid posted notices[]</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>notice-location</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Notice location</t>
+        </is>
+      </c>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Location where the notice was posted</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -5386,7 +5410,7 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5395,27 +5419,27 @@
       <c r="B100" s="2" t="n"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>valid-posted-notices</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Valid posted notices[]</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>newspaper-name</t>
+          <t>notice-posted-date</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Notice posted date</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -5424,12 +5448,12 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when the notice was posted</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -5443,27 +5467,27 @@
       <c r="B101" s="2" t="n"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>invalid-posted-notices</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Invalid posted notices[]</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>publication-date</t>
+          <t>parish-ward</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Publication date</t>
+          <t>Parish or ward</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -5472,12 +5496,12 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>Parish or ward where the notice was posted</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -5491,38 +5515,46 @@
       <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>invalid-posted-notices</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr"/>
+          <t>Invalid posted notices[]</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>notice-location</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Notice location</t>
+        </is>
+      </c>
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Location where the notice was posted</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5531,38 +5563,46 @@
       <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>applicant-signature</t>
+          <t>invalid-posted-notices</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
+          <t>Invalid posted notices[]</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>notice-posted-date</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Notice posted date</t>
+        </is>
+      </c>
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Date when the notice was posted</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5571,17 +5611,17 @@
       <c r="B104" s="2" t="n"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>agent-signature</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Steps taken</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
@@ -5592,7 +5632,7 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>Steps taken to protect or replace notices that were removed, obscured or defaced</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -5611,81 +5651,89 @@
       <c r="B105" s="2" t="n"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Access and rights of way</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>access-rights-of-way</t>
-        </is>
-      </c>
+      <c r="A106" s="2" t="n"/>
+      <c r="B106" s="2" t="n"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>new-altered-vehicle</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>New or altered vehicle access</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>publication-date</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -5699,17 +5747,17 @@
       <c r="B107" s="2" t="n"/>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>new-altered-pedestrian</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>New or altered pedestrian access</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
@@ -5720,12 +5768,12 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -5739,17 +5787,17 @@
       <c r="B108" s="2" t="n"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>new-right-of-way</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>New right of way</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
@@ -5760,12 +5808,12 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Will new public rights of way be provided within or adjacent to the site</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -5779,17 +5827,17 @@
       <c r="B109" s="2" t="n"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>new-public-road</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>New public road</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
@@ -5800,12 +5848,12 @@
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>Will new public roads be provided within the site</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -5815,8 +5863,16 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n"/>
-      <c r="B110" s="2" t="n"/>
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Access and rights of way</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>access-rights-of-way</t>
+        </is>
+      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
@@ -5824,12 +5880,12 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>temp-right-of-way</t>
+          <t>new-altered-vehicle</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Temporary right of way changes</t>
+          <t>New or altered vehicle access</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
@@ -5840,7 +5896,7 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>Are temporary changes to rights of way needed while the site is worked</t>
+          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -5864,12 +5920,12 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>future-new-right-of-way</t>
+          <t>new-altered-pedestrian</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Future new right of way</t>
+          <t>New or altered pedestrian access</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
@@ -5880,7 +5936,7 @@
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>Will new public rights of way be provided after extraction?</t>
+          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
@@ -5904,36 +5960,28 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>new-right-of-way</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>New right of way</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Will new public rights of way be provided within or adjacent to the site</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -5943,53 +5991,37 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>Plans, drawings and supporting materials</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>plans-drawings-supporting-materials</t>
-        </is>
-      </c>
+      <c r="A113" s="2" t="n"/>
+      <c r="B113" s="2" t="n"/>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Additional materials and specifications that form part of the planning application</t>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>new-public-road</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>New public road</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Will new public roads be provided within the site</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -6003,17 +6035,17 @@
       <c r="B114" s="2" t="n"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Additional materials and specifications that form part of the planning application</t>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>inspection-address</t>
+          <t>temp-right-of-way</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Inspection address</t>
+          <t>Temporary right of way changes</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
@@ -6024,12 +6056,12 @@
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>Full postal address where supporting material can be inspected</t>
+          <t>Are temporary changes to rights of way needed while the site is worked</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -6039,29 +6071,21 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A115" s="2" t="n"/>
+      <c r="B115" s="2" t="n"/>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>future-new-right-of-way</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Future new right of way</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
@@ -6072,12 +6096,12 @@
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Will new public rights of way be provided after extraction?</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -6091,28 +6115,36 @@
       <c r="B116" s="2" t="n"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
@@ -6122,30 +6154,46 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n"/>
-      <c r="B117" s="2" t="n"/>
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Plans, drawings and supporting materials</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>plans-drawings-supporting-materials</t>
+        </is>
+      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Additional materials and specifications that form part of the planning application</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
+          <t>supporting-documents</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
           <t>reference</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr"/>
       <c r="I117" s="2" t="inlineStr"/>
       <c r="J117" s="2" t="inlineStr"/>
@@ -6162,7 +6210,7 @@
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6171,17 +6219,17 @@
       <c r="B118" s="2" t="n"/>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Additional materials and specifications that form part of the planning application</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>inspection-address</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Inspection address</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
@@ -6192,23 +6240,31 @@
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Full postal address where supporting material can be inspected</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n"/>
-      <c r="B119" s="2" t="n"/>
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -6216,12 +6272,12 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
@@ -6232,68 +6288,52 @@
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A120" s="2" t="n"/>
+      <c r="B120" s="2" t="n"/>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>site-boundary</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Officer name</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr"/>
       <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -6307,36 +6347,28 @@
       <c r="B121" s="2" t="n"/>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>address-text</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr"/>
       <c r="I121" s="2" t="inlineStr"/>
       <c r="J121" s="2" t="inlineStr"/>
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
@@ -6355,41 +6387,33 @@
       <c r="B122" s="2" t="n"/>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Advice date</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr"/>
       <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -6403,41 +6427,33 @@
       <c r="B123" s="2" t="n"/>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>easting</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>Easting</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr"/>
       <c r="I123" s="2" t="inlineStr"/>
       <c r="J123" s="2" t="inlineStr"/>
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -6447,8 +6463,16 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n"/>
-      <c r="B124" s="2" t="n"/>
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -6466,12 +6490,12 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>site-boundary</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr"/>
@@ -6480,12 +6504,12 @@
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -6514,12 +6538,12 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr"/>
@@ -6528,12 +6552,12 @@
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -6562,12 +6586,12 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr"/>
@@ -6576,12 +6600,12 @@
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -6610,12 +6634,12 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr"/>
@@ -6624,12 +6648,12 @@
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -6658,12 +6682,12 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr"/>
@@ -6672,12 +6696,12 @@
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -6687,39 +6711,31 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>Site ownership</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>site-ownership</t>
-        </is>
-      </c>
+      <c r="A129" s="2" t="n"/>
+      <c r="B129" s="2" t="n"/>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>site-owner</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Site owner</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>fullname</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr"/>
@@ -6728,17 +6744,17 @@
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6747,27 +6763,27 @@
       <c r="B130" s="2" t="n"/>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>site-owner</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Site owner</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr"/>
@@ -6776,17 +6792,17 @@
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6795,28 +6811,36 @@
       <c r="B131" s="2" t="n"/>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>applicant-interest</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr"/>
-      <c r="G131" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
       <c r="H131" s="2" t="inlineStr"/>
       <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>Description of the applicant's interest in the land</t>
+          <t>A text description providing details about the subject.</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
@@ -6826,7 +6850,7 @@
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6835,28 +6859,36 @@
       <c r="B132" s="2" t="n"/>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>applicant-interest-adjoining-land</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest adjoining land</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr"/>
-      <c r="G132" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>uprns</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="H132" s="2" t="inlineStr"/>
       <c r="I132" s="2" t="inlineStr"/>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>Description of the applicant's interest in the adjacent land</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
@@ -6866,50 +6898,58 @@
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Site Visit Details</t>
+          <t>Site ownership</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>site-visit</t>
+          <t>site-ownership</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>site-owner</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr"/>
-      <c r="G133" s="2" t="inlineStr"/>
+          <t>Site owner</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="H133" s="2" t="inlineStr"/>
       <c r="I133" s="2" t="inlineStr"/>
       <c r="J133" s="2" t="inlineStr"/>
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
@@ -6923,33 +6963,41 @@
       <c r="B134" s="2" t="n"/>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>site-owner</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr"/>
-      <c r="G134" s="2" t="inlineStr"/>
+          <t>Site owner</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="H134" s="2" t="inlineStr"/>
       <c r="I134" s="2" t="inlineStr"/>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -6963,17 +7011,17 @@
       <c r="B135" s="2" t="n"/>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>applicant-interest</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Applicant interest</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr"/>
@@ -6984,7 +7032,7 @@
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Details of the applicant's interest in the land</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
@@ -6994,7 +7042,7 @@
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7003,36 +7051,28 @@
       <c r="B136" s="2" t="n"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>applicant-interest-adjoining-land</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>fullname</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Applicant interest adjoining land</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr"/>
       <c r="I136" s="2" t="inlineStr"/>
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Description of the applicant's interest in the adjacent land</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
@@ -7047,8 +7087,16 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n"/>
-      <c r="B137" s="2" t="n"/>
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -7056,36 +7104,28 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr"/>
       <c r="I137" s="2" t="inlineStr"/>
       <c r="J137" s="2" t="inlineStr"/>
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -7104,36 +7144,28 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr"/>
       <c r="I138" s="2" t="inlineStr"/>
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -7143,29 +7175,21 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>Storage facilities</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>storage-facilities</t>
-        </is>
-      </c>
+      <c r="A139" s="2" t="n"/>
+      <c r="B139" s="2" t="n"/>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>For oil and gas extraction developments, how chemicals will be stored</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>storage-facilities-description</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Storage facilities description</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
@@ -7176,7 +7200,7 @@
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>Details and proposed facilities for the storage of oil, fuel and chemicals and the proposed means of their protection</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
@@ -7186,50 +7210,50 @@
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Trade effluent</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>trade-effluent</t>
-        </is>
-      </c>
+      <c r="A140" s="2" t="n"/>
+      <c r="B140" s="2" t="n"/>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>is-disposal-required</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Disposal required</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr"/>
-      <c r="G140" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="H140" s="2" t="inlineStr"/>
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -7243,28 +7267,36 @@
       <c r="B141" s="2" t="n"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr"/>
-      <c r="G141" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="H141" s="2" t="inlineStr"/>
       <c r="I141" s="2" t="inlineStr"/>
       <c r="J141" s="2" t="inlineStr"/>
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
@@ -7274,50 +7306,50 @@
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Trees and hedges information</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>trees-hedges</t>
-        </is>
-      </c>
+      <c r="A142" s="2" t="n"/>
+      <c r="B142" s="2" t="n"/>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>trees-on-site</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Trees on site</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr"/>
-      <c r="G142" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H142" s="2" t="inlineStr"/>
       <c r="I142" s="2" t="inlineStr"/>
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges are present on the proposed development site</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -7327,21 +7359,29 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n"/>
-      <c r="B143" s="2" t="n"/>
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Storage facilities</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>storage-facilities</t>
+        </is>
+      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+          <t>For oil and gas extraction developments, how chemicals will be stored</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>trees-on-adj-land</t>
+          <t>storage-facilities-description</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Trees on adjacent land</t>
+          <t>Storage facilities description</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
@@ -7352,12 +7392,12 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
+          <t>Details and proposed facilities for the storage of oil, fuel and chemicals and the proposed means of their protection</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -7369,28 +7409,27 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Oil and gas permission types</t>
+          <t>Trade effluent</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>oilgas-permission-type</t>
+          <t>trade-effluent</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
-</t>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>oilgas-permission-types</t>
+          <t>is-disposal-required</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Oil and gas permission types[]</t>
+          <t>Disposal required</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
@@ -7401,12 +7440,12 @@
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>List of permission types being applied for</t>
+          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -7420,37 +7459,28 @@
       <c r="B145" s="2" t="n"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
-</t>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>related-permissions</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Related permissions[]</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr"/>
       <c r="I145" s="2" t="inlineStr"/>
       <c r="J145" s="2" t="inlineStr"/>
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application that permission was received for</t>
+          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
@@ -7460,51 +7490,50 @@
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n"/>
-      <c r="B146" s="2" t="n"/>
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>trees-hedges</t>
+        </is>
+      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
-</t>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>related-permissions</t>
+          <t>trees-on-site</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Related permissions[]</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>oilgas-permission-type</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>Oil and gas permission type</t>
-        </is>
-      </c>
+          <t>Trees on site</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr"/>
       <c r="I146" s="2" t="inlineStr"/>
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>An oil and gas related permission type</t>
+          <t>Whether trees or hedges are present on the proposed development site</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -7518,42 +7547,33 @@
       <c r="B147" s="2" t="n"/>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
-</t>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>related-permissions</t>
+          <t>trees-on-adj-land</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Related permissions[]</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>decision-date</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>Decision date</t>
-        </is>
-      </c>
+          <t>Trees on adjacent land</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr"/>
       <c r="I147" s="2" t="inlineStr"/>
       <c r="J147" s="2" t="inlineStr"/>
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -7563,8 +7583,16 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n"/>
-      <c r="B148" s="2" t="n"/>
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Oil and gas permission types</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>oilgas-permission-type</t>
+        </is>
+      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
@@ -7573,41 +7601,33 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>related-permissions</t>
+          <t>oilgas-permission-types</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Related permissions[]</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>condition-number</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t>Condition number</t>
-        </is>
-      </c>
+          <t>Oil and gas permission types[]</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr"/>
       <c r="I148" s="2" t="inlineStr"/>
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>Number of any condition being breached</t>
+          <t>List of permission types being applied for</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7622,23 +7642,31 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>other-details</t>
+          <t>related-permissions</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Other details</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr"/>
-      <c r="G149" s="2" t="inlineStr"/>
+          <t>Related permissions[]</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H149" s="2" t="inlineStr"/>
       <c r="I149" s="2" t="inlineStr"/>
       <c r="J149" s="2" t="inlineStr"/>
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>Explanation if other ground is selected</t>
+          <t>The reference for the related application that permission was received for</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
@@ -7648,7 +7676,7 @@
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7663,28 +7691,36 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>will-consolidate-permissions</t>
+          <t>related-permissions</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Will consolidate permissions</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr"/>
-      <c r="G150" s="2" t="inlineStr"/>
+          <t>Related permissions[]</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>oilgas-permission-type</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Oil and gas permission type</t>
+        </is>
+      </c>
       <c r="H150" s="2" t="inlineStr"/>
       <c r="I150" s="2" t="inlineStr"/>
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant looking to consolidate permissions?</t>
+          <t>An oil and gas related permission type</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -7704,33 +7740,41 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>details</t>
+          <t>related-permissions</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr"/>
-      <c r="G151" s="2" t="inlineStr"/>
+          <t>Related permissions[]</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>decision-date</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Decision date</t>
+        </is>
+      </c>
       <c r="H151" s="2" t="inlineStr"/>
       <c r="I151" s="2" t="inlineStr"/>
       <c r="J151" s="2" t="inlineStr"/>
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>Details about the consolidation or update of permissions</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7745,22 +7789,22 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>related-proposals</t>
+          <t>related-permissions</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Related proposals[]</t>
+          <t>Related permissions[]</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>condition-number</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Condition number</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr"/>
@@ -7769,7 +7813,7 @@
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>Number of any condition being breached</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
@@ -7779,7 +7823,7 @@
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7794,41 +7838,33 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>related-proposals</t>
+          <t>other-details</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Related proposals[]</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>application-type</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>Application type</t>
-        </is>
-      </c>
+          <t>Other details</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr"/>
       <c r="I153" s="2" t="inlineStr"/>
       <c r="J153" s="2" t="inlineStr"/>
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>The type of planning application</t>
+          <t>Explanation if other ground is selected</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7843,36 +7879,28 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>related-proposals</t>
+          <t>will-consolidate-permissions</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Related proposals[]</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>decision-date</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>Decision date</t>
-        </is>
-      </c>
+          <t>Will consolidate permissions</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr"/>
       <c r="I154" s="2" t="inlineStr"/>
       <c r="J154" s="2" t="inlineStr"/>
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>Is the applicant looking to consolidate permissions?</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -7882,29 +7910,22 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>Development type</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>dev-type</t>
-        </is>
-      </c>
+      <c r="A155" s="2" t="n"/>
+      <c r="B155" s="2" t="n"/>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
+          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
+</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>development-phase</t>
+          <t>details</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Development phase</t>
+          <t>Details</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr"/>
@@ -7915,17 +7936,17 @@
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>Phases of oil and gas development the application covers</t>
+          <t>Details about the consolidation or update of permissions</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7934,28 +7955,37 @@
       <c r="B156" s="2" t="n"/>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
+          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
+</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>related-proposals</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Development description</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr"/>
-      <c r="G156" s="2" t="inlineStr"/>
+          <t>Related proposals[]</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H156" s="2" t="inlineStr"/>
       <c r="I156" s="2" t="inlineStr"/>
       <c r="J156" s="2" t="inlineStr"/>
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>Brief description of the development, including main oils, gases, and machinery</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
@@ -7974,33 +8004,42 @@
       <c r="B157" s="2" t="n"/>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
+          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
+</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>quantity-cubic-metres</t>
+          <t>related-proposals</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Quantity cubic metres</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="inlineStr"/>
-      <c r="G157" s="2" t="inlineStr"/>
+          <t>Related proposals[]</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>application-type</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Application type</t>
+        </is>
+      </c>
       <c r="H157" s="2" t="inlineStr"/>
       <c r="I157" s="2" t="inlineStr"/>
       <c r="J157" s="2" t="inlineStr"/>
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>Quantity of oil or gas involved in cubic metres</t>
+          <t>The type of planning application</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -8014,44 +8053,61 @@
       <c r="B158" s="2" t="n"/>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
+          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
+</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>permission-period-years</t>
+          <t>related-proposals</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Permission period years</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr"/>
-      <c r="G158" s="2" t="inlineStr"/>
+          <t>Related proposals[]</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>decision-date</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Decision date</t>
+        </is>
+      </c>
       <c r="H158" s="2" t="inlineStr"/>
       <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>Period of permission sought in years</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n"/>
-      <c r="B159" s="2" t="n"/>
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Development type</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>dev-type</t>
+        </is>
+      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
@@ -8059,12 +8115,12 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>hydrocarbon-licence-block</t>
+          <t>development-phase</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Hydrocarbon licence block</t>
+          <t>Development phase</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
@@ -8075,12 +8131,12 @@
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>Hydrocarbon licence block where the development is located</t>
+          <t>Phases of oil and gas development the application covers</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -8099,12 +8155,12 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>surface-site-area-hectares</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Surface site area hectares</t>
+          <t>Development description</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
@@ -8115,17 +8171,17 @@
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>Surface site area in hectares</t>
+          <t>Brief description of the development, including main oils, gases, and machinery</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8139,12 +8195,12 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>site-hectares-provided-by</t>
+          <t>quantity-cubic-metres</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Site hectares provided by</t>
+          <t>Quantity cubic metres</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr"/>
@@ -8155,17 +8211,17 @@
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site hectares value (applicant or system)</t>
+          <t>Quantity of oil or gas involved in cubic metres</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8179,12 +8235,12 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>environmental-statement</t>
+          <t>permission-period-years</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Environmental statement</t>
+          <t>Permission period years</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
@@ -8195,17 +8251,17 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>Is an Environmental Statement attached to the application</t>
+          <t>Period of permission sought in years</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8219,12 +8275,12 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>environmental-statement-reference</t>
+          <t>hydrocarbon-licence-block</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Environmental statement reference</t>
+          <t>Hydrocarbon licence block</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr"/>
@@ -8235,7 +8291,7 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>Reference to the environmental statement document</t>
+          <t>Hydrocarbon licence block where the development is located</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
@@ -8245,34 +8301,26 @@
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>Voluntary agreement</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>vol-agreement</t>
-        </is>
-      </c>
+      <c r="A164" s="2" t="n"/>
+      <c r="B164" s="2" t="n"/>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Details of any voluntary agreements made as part of an oil and gas extraction application.</t>
+          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>draft-agreement-included</t>
+          <t>surface-site-area-hectares</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Draft agreement included</t>
+          <t>Surface site area hectares</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr"/>
@@ -8283,17 +8331,17 @@
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>Has an outline or draft agreement been included? (True / False)</t>
+          <t>Surface site area in hectares</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8302,17 +8350,17 @@
       <c r="B165" s="2" t="n"/>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Details of any voluntary agreements made as part of an oil and gas extraction application.</t>
+          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>agreement-summary</t>
+          <t>site-hectares-provided-by</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Agreement summary</t>
+          <t>Site hectares provided by</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr"/>
@@ -8323,15 +8371,183 @@
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
+          <t>Who provided the site hectares value (applicant or system)</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n"/>
+      <c r="B166" s="2" t="n"/>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>environmental-statement</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Environmental statement</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr"/>
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>Is an Environmental Statement attached to the application</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n"/>
+      <c r="B167" s="2" t="n"/>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>environmental-statement-reference</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Environmental statement reference</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr"/>
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>Reference to the environmental statement document</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Voluntary agreement</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>vol-agreement</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Details of any voluntary agreements made as part of an oil and gas extraction application.</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>draft-agreement-included</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Draft agreement included</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr"/>
+      <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>Has an outline or draft agreement been included? (True / False)</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n"/>
+      <c r="B169" s="2" t="n"/>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Details of any voluntary agreements made as part of an oil and gas extraction application.</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>agreement-summary</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Agreement summary</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr"/>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr"/>
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
           <t>Summary of the agreement</t>
         </is>
       </c>
-      <c r="M165" s="2" t="inlineStr">
+      <c r="M169" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N165" s="2" t="inlineStr">
+      <c r="N169" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -8339,66 +8555,66 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="B35:B40"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="B65"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="B91:B105"/>
-    <mergeCell ref="A83:A90"/>
-    <mergeCell ref="B139"/>
-    <mergeCell ref="A59:A64"/>
-    <mergeCell ref="B50:B53"/>
-    <mergeCell ref="B66:B75"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A76:A80"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B59:B64"/>
-    <mergeCell ref="A41:A46"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="A115:A119"/>
-    <mergeCell ref="A120:A128"/>
-    <mergeCell ref="A58"/>
-    <mergeCell ref="A144:A154"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="B54"/>
-    <mergeCell ref="A113:A114"/>
-    <mergeCell ref="B47:B49"/>
-    <mergeCell ref="B76:B80"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="A106:A112"/>
-    <mergeCell ref="A133:A138"/>
-    <mergeCell ref="A155:A163"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="B23:B30"/>
-    <mergeCell ref="B115:B119"/>
-    <mergeCell ref="B58"/>
-    <mergeCell ref="A91:A105"/>
-    <mergeCell ref="A129:A132"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="A65"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="A54"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="A66:A75"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="B106:B112"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="A35:A40"/>
-    <mergeCell ref="B155:B163"/>
-    <mergeCell ref="B83:B90"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="B113:B114"/>
-    <mergeCell ref="A139"/>
-    <mergeCell ref="B144:B154"/>
-    <mergeCell ref="B129:B132"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="B133:B138"/>
-    <mergeCell ref="A23:A30"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="B120:B128"/>
-    <mergeCell ref="B41:B46"/>
+    <mergeCell ref="B119:B123"/>
+    <mergeCell ref="B51:B54"/>
+    <mergeCell ref="B143"/>
+    <mergeCell ref="B148:B158"/>
+    <mergeCell ref="B55"/>
+    <mergeCell ref="A124:A132"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A24:A31"/>
+    <mergeCell ref="A60:A65"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="A36:A41"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="A67:A76"/>
+    <mergeCell ref="A137:A142"/>
+    <mergeCell ref="B117:B118"/>
+    <mergeCell ref="A143"/>
+    <mergeCell ref="A159:A167"/>
+    <mergeCell ref="B92:B109"/>
+    <mergeCell ref="A59"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="B42:B47"/>
+    <mergeCell ref="A77:A81"/>
+    <mergeCell ref="B124:B132"/>
+    <mergeCell ref="B59"/>
+    <mergeCell ref="A133:A136"/>
+    <mergeCell ref="B66"/>
+    <mergeCell ref="A84:A91"/>
+    <mergeCell ref="B110:B116"/>
+    <mergeCell ref="A32:A35"/>
+    <mergeCell ref="B67:B76"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B60:B65"/>
+    <mergeCell ref="A92:A109"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B168:B169"/>
+    <mergeCell ref="B137:B142"/>
+    <mergeCell ref="A66"/>
+    <mergeCell ref="B133:B136"/>
+    <mergeCell ref="B84:B91"/>
+    <mergeCell ref="A110:A116"/>
+    <mergeCell ref="A119:A123"/>
+    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="A42:A47"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B77:B81"/>
+    <mergeCell ref="A148:A158"/>
+    <mergeCell ref="A55"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B159:B167"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="B24:B31"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="B144:B145"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas-verbose.xlsx
+++ b/generated/spreadsheet/verbose/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N169"/>
+  <dimension ref="A1:N172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -440,9 +440,9 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -1980,19 +1980,27 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>address-text</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2036,19 +2044,27 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2082,21 +2098,37 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2130,12 +2162,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -2144,12 +2176,12 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2159,56 +2191,64 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2216,31 +2256,23 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2274,29 +2306,21 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -2306,7 +2330,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2340,24 +2364,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -2367,64 +2391,72 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2442,29 +2474,21 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2474,7 +2498,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2508,19 +2532,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2530,7 +2554,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2564,19 +2588,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2620,19 +2644,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2676,77 +2700,101 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Postcode for a contact address or site</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>flood-risk-assessment</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Results of any flood risk assessments made for the development site</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>flood-risk-area</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk area</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>Is the site within an area at risk of flooding?</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2755,57 +2803,89 @@
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Unique Property Reference Number for a property</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>flood-risk-assessment</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
           <t>Results of any flood risk assessments made for the development site</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>data-provided-by</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Data provided by</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Results of any flood risk assessments made for the development site</t>
-        </is>
-      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>flood-risk-assessment</t>
+          <t>flood-risk-area</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Flood risk area</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -2816,17 +2896,17 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2840,12 +2920,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>within-20m-watercourse</t>
+          <t>data-provided-by</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -2856,17 +2936,17 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2880,12 +2960,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>increases-flood-risk</t>
+          <t>flood-risk-assessment</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2896,17 +2976,17 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2920,12 +3000,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>surface-water-disposal</t>
+          <t>within-20m-watercourse</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2936,12 +3016,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -2951,29 +3031,21 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Results of any flood risk assessments made for the development site</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>increases-flood-risk</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -2984,7 +3056,7 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -3003,17 +3075,17 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Results of any flood risk assessments made for the development site</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>surface-water-disposal</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Surface water disposal[]</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -3024,23 +3096,31 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Reference to the applicant or agent with the conflict</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -3048,12 +3128,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3064,44 +3144,36 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity, geological and archaeological conservation</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>bio-geo-arch-con</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>protected-species-impact</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Protected species impact</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -3112,17 +3184,17 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of protected and priority species being affected?</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3131,17 +3203,17 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>biodiversity-features-impact</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity features impact</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -3152,23 +3224,31 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="2" t="n"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity, geological and archaeological conservation</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>bio-geo-arch-con</t>
+        </is>
+      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
@@ -3176,12 +3256,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>geological-features-impact</t>
+          <t>protected-species-impact</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Geological features impact</t>
+          <t>Protected species impact</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -3192,7 +3272,7 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
+          <t>Where is there a likelihood of protected and priority species being affected?</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -3216,12 +3296,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>archaeological-features-impact</t>
+          <t>biodiversity-features-impact</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Archaeological features impact</t>
+          <t>Biodiversity features impact</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
@@ -3232,7 +3312,7 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of archaeological conservation importance being affected?</t>
+          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -3247,29 +3327,21 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>geological-features-impact</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Geological features impact</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
@@ -3280,12 +3352,12 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -3295,29 +3367,21 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>archaeological-features-impact</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Archaeological features impact</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3328,12 +3392,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Where is there a likelihood of features of archaeological conservation importance being affected?</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -3343,21 +3407,29 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n"/>
-      <c r="B57" s="2" t="n"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -3368,12 +3440,12 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -3383,8 +3455,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="2" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -3392,12 +3472,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -3408,12 +3488,12 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -3423,29 +3503,21 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Designated areas</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>designated-areas</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Details of any 'designated area' the develpoment site is on, such as a Conservation Area or National Park.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>designations</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Designations[]</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
@@ -3456,12 +3528,12 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>List of designated areas that apply to the site</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -3471,53 +3543,37 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>employment</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>existing-employees</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>full-time</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
+          <t>Declaration date</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -3527,45 +3583,45 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="2" t="n"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Designated areas</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>designated-areas</t>
+        </is>
+      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
+          <t>Details of any 'designated area' the develpoment site is on, such as a Conservation Area or National Park.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>existing-employees</t>
+          <t>designations</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>part-time</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Part-time</t>
-        </is>
-      </c>
+          <t>Designations[]</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>List of designated areas that apply to the site</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -3575,8 +3631,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n"/>
-      <c r="B62" s="2" t="n"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>How the proposed development will impact existing and proposed employee numbers</t>
@@ -3594,12 +3658,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>total-fte</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -3608,12 +3672,12 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -3632,22 +3696,22 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>proposed-employees</t>
+          <t>existing-employees</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>full-time</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -3656,7 +3720,7 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -3680,22 +3744,22 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>proposed-employees</t>
+          <t>existing-employees</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>total-fte</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -3704,12 +3768,12 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3738,12 +3802,12 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>total-fte</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -3752,12 +3816,12 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -3767,45 +3831,45 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Equipment and method</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>equip-method</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>How oil and gas will be extracted as part of the proposed development.</t>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>equipment-plan</t>
+          <t>proposed-employees</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Equipment plan</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
+          <t>Proposed employees</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>part-time</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Part-time</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Details of equipment to be used as part of the application including the maximum height and type of drilling rig to be used</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -3815,39 +3879,31 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>existing-use</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>How the site is currently being used.</t>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>existing-use-details</t>
+          <t>proposed-employees</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>total-fte</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -3856,12 +3912,12 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -3871,40 +3927,40 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Equipment and method</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>equip-method</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>How the site is currently being used.</t>
+          <t>How oil and gas will be extracted as part of the proposed development.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>existing-use-details</t>
+          <t>equipment-plan</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>use-details</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Use details</t>
-        </is>
-      </c>
+          <t>Equipment plan</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>Details of equipment to be used as part of the application including the maximum height and type of drilling rig to be used</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -3914,13 +3970,21 @@
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n"/>
-      <c r="B69" s="2" t="n"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>existing-use</t>
+        </is>
+      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>How the site is currently being used.</t>
@@ -3938,12 +4002,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>land-part</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Land part</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -3952,12 +4016,12 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -3976,33 +4040,41 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>site-vacant</t>
+          <t>existing-use-details</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>use-details</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Use details</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4016,23 +4088,31 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>last-use-details</t>
+          <t>existing-use-details</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>land-part</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Land part</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -4042,7 +4122,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4136,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>last-use-end-date</t>
+          <t>site-vacant</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Site vacant</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -4072,17 +4152,17 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4096,12 +4176,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>is-contaminated-land</t>
+          <t>last-use-details</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -4112,17 +4192,17 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4216,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>is-suspected-contaminated-land</t>
+          <t>last-use-end-date</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -4152,17 +4232,17 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4176,12 +4256,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>proposed-use-contamination-risk</t>
+          <t>is-contaminated-land</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -4192,7 +4272,7 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -4216,12 +4296,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>contamination-assessment</t>
+          <t>is-suspected-contaminated-land</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -4232,44 +4312,36 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Foul sewage disposal</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>foul-sewage</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>How waste water will leave the property as part of the proposed development</t>
+          <t>How the site is currently being used.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>has-new-disposal-arrangements</t>
+          <t>proposed-use-contamination-risk</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Has new disposal arrangements</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -4280,7 +4352,7 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include any new foul sewage disposal arrangments</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -4299,17 +4371,17 @@
       <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>How waste water will leave the property as part of the proposed development</t>
+          <t>How the site is currently being used.</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>foul-sewage-disposal-types</t>
+          <t>contamination-assessment</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Foul sewage disposal types[]</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -4320,12 +4392,12 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>List of ways foul sewage will be disposed of</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -4335,8 +4407,16 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n"/>
-      <c r="B79" s="2" t="n"/>
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Foul sewage disposal</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>foul-sewage</t>
+        </is>
+      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>How waste water will leave the property as part of the proposed development</t>
@@ -4344,12 +4424,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>produce-foul-sewage</t>
+          <t>has-new-disposal-arrangements</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Produce foul sewage</t>
+          <t>Has new disposal arrangements</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -4360,7 +4440,7 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposed development will produce any foul sewage</t>
+          <t>Does the proposal include any new foul sewage disposal arrangments</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -4384,12 +4464,12 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>connect-to-drainage-system-oil-gas</t>
+          <t>foul-sewage-disposal-types</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Connect to drainage system (oil and gas)</t>
+          <t>Foul sewage disposal types[]</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -4400,7 +4480,7 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal needs to connect to the existing drainage system (oil and gas applications)</t>
+          <t>List of ways foul sewage will be disposed of</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -4410,7 +4490,7 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4424,36 +4504,28 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>produce-foul-sewage</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Produce foul sewage</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Whether the proposed development will produce any foul sewage</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -4463,29 +4535,21 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substances</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>haz-substances</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Details of hazardous substances requiring consent used as part of the development</t>
+          <t>How waste water will leave the property as part of the proposed development</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>hazardous-sub-consent-req</t>
+          <t>connect-to-drainage-system-oil-gas</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance consent required</t>
+          <t>Connect to drainage system (oil and gas)</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -4496,12 +4560,12 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the use or storage of any substances requiring hazardous substances consent</t>
+          <t>Whether the proposal needs to connect to the existing drainage system (oil and gas applications)</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -4515,28 +4579,36 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Details of hazardous substances requiring consent used as part of the development</t>
+          <t>How waste water will leave the property as part of the proposed development</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>hazardous-sub-consent-details</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance consent details</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Details of hazardous substance consent requirements</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -4546,58 +4618,50 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation</t>
+          <t>Hazardous substances</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>hrs-operation</t>
+          <t>haz-substances</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+          <t>Details of hazardous substances requiring consent used as part of the development</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>hours-of-operation</t>
+          <t>hazardous-sub-consent-req</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>use</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
+          <t>Hazardous substance consent required</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Does the proposal involve the use or storage of any substances requiring hazardous substances consent</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -4611,36 +4675,28 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+          <t>Details of hazardous substances requiring consent used as part of the development</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>hours-of-operation</t>
+          <t>hazardous-sub-consent-details</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>use-other</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>Use other</t>
-        </is>
-      </c>
+          <t>Hazardous substance consent details</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Details of hazardous substance consent requirements</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -4655,8 +4711,16 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n"/>
-      <c r="B86" s="2" t="n"/>
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>hrs-operation</t>
+        </is>
+      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
@@ -4674,29 +4738,21 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>operational-times</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>schedule-days</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>Schedule days[]</t>
-        </is>
-      </c>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>List of days or day categories that a schedule entry applies to</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -4730,34 +4786,26 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>operational-times</t>
+          <t>use-other</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
+          <t>Use other</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -4796,32 +4844,24 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>time-ranges</t>
+          <t>schedule-days</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>open-time</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>Open time</t>
-        </is>
-      </c>
+          <t>Schedule days[]</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -4860,37 +4900,29 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>time-ranges</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>close-time</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>Close time</t>
-        </is>
-      </c>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4914,31 +4946,47 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>hours-not-known</t>
+          <t>operational-times</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Hours not known</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr"/>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>time-ranges</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>open-time</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Open time</t>
+        </is>
+      </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Applicant states they do not know the hours of operation</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4952,23 +5000,47 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>additional-information</t>
+          <t>hours-of-operation</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Additional information</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-      <c r="K91" s="2" t="inlineStr"/>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>operational-times</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>time-ranges</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>close-time</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Close time</t>
+        </is>
+      </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Any additional information (such as hours of use of other machinery within the site-generators, pumps, etc)</t>
+          <t>Closing time</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -4978,66 +5050,50 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Oil and gas ownership and notices</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>oil-gas-ownership-notices</t>
-        </is>
-      </c>
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>hours-of-operation</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
+          <t>Hours of operation[]</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>hours-not-known</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Hours not known</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -5051,44 +5107,28 @@
       <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>additional-information</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>first-name</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
+          <t>Additional information</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>Any additional information (such as hours of use of other machinery within the site-generators, pumps, etc)</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -5098,13 +5138,21 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n"/>
-      <c r="B94" s="2" t="n"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Oil and gas ownership and notices</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>oil-gas-ownership-notices</t>
+        </is>
+      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
@@ -5132,19 +5180,19 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -5154,7 +5202,7 @@
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5188,19 +5236,19 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -5244,19 +5292,19 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -5266,7 +5314,7 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5290,31 +5338,47 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>notice-served-date</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Notice served date</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr"/>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-      <c r="K97" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5328,31 +5392,47 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>valid-posted-notices</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Valid posted notices[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>parish-ward</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Parish or ward</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-      <c r="K98" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Parish or ward where the notice was posted</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -5362,7 +5442,7 @@
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5376,31 +5456,47 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>valid-posted-notices</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Valid posted notices[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>notice-location</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Notice location</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-      <c r="K99" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>Location where the notice was posted</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -5410,7 +5506,7 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5424,22 +5520,22 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>valid-posted-notices</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Valid posted notices[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>notice-posted-date</t>
+          <t>notice-served-date</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Notice posted date</t>
+          <t>Notice served date</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -5448,7 +5544,7 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was posted</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -5458,7 +5554,7 @@
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5472,12 +5568,12 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>invalid-posted-notices</t>
+          <t>valid-posted-notices</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Invalid posted notices[]</t>
+          <t>Valid posted notices[]</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -5520,12 +5616,12 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>invalid-posted-notices</t>
+          <t>valid-posted-notices</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Invalid posted notices[]</t>
+          <t>Valid posted notices[]</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -5568,12 +5664,12 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>invalid-posted-notices</t>
+          <t>valid-posted-notices</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Invalid posted notices[]</t>
+          <t>Valid posted notices[]</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -5616,23 +5712,31 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>invalid-posted-notices</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="inlineStr"/>
+          <t>Invalid posted notices[]</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>parish-ward</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Parish or ward</t>
+        </is>
+      </c>
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Steps taken to protect or replace notices that were removed, obscured or defaced</t>
+          <t>Parish or ward where the notice was posted</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -5642,7 +5746,7 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5656,22 +5760,22 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>invalid-posted-notices</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Invalid posted notices[]</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>newspaper-name</t>
+          <t>notice-location</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Notice location</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr"/>
@@ -5680,7 +5784,7 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Location where the notice was posted</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -5704,22 +5808,22 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>invalid-posted-notices</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Invalid posted notices[]</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>publication-date</t>
+          <t>notice-posted-date</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Publication date</t>
+          <t>Notice posted date</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
@@ -5728,7 +5832,7 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>Date when the notice was posted</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -5752,12 +5856,12 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Steps taken</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
@@ -5768,7 +5872,7 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Steps taken to protect or replace notices that were removed, obscured or defaced</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
@@ -5778,7 +5882,7 @@
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5792,28 +5896,36 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -5832,23 +5944,31 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>publication-date</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="H109" s="2" t="inlineStr"/>
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
@@ -5863,29 +5983,21 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Access and rights of way</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>access-rights-of-way</t>
-        </is>
-      </c>
+      <c r="A110" s="2" t="n"/>
+      <c r="B110" s="2" t="n"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>new-altered-vehicle</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>New or altered vehicle access</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
@@ -5896,12 +6008,12 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -5915,17 +6027,17 @@
       <c r="B111" s="2" t="n"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>new-altered-pedestrian</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>New or altered pedestrian access</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
@@ -5936,12 +6048,12 @@
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -5955,17 +6067,17 @@
       <c r="B112" s="2" t="n"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>new-right-of-way</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>New right of way</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
@@ -5976,12 +6088,12 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>Will new public rights of way be provided within or adjacent to the site</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -5991,8 +6103,16 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n"/>
-      <c r="B113" s="2" t="n"/>
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Access and rights of way</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>access-rights-of-way</t>
+        </is>
+      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
@@ -6000,12 +6120,12 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>new-public-road</t>
+          <t>new-altered-vehicle</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>New public road</t>
+          <t>New or altered vehicle access</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
@@ -6016,7 +6136,7 @@
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>Will new public roads be provided within the site</t>
+          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
@@ -6040,12 +6160,12 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>temp-right-of-way</t>
+          <t>new-altered-pedestrian</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Temporary right of way changes</t>
+          <t>New or altered pedestrian access</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
@@ -6056,7 +6176,7 @@
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>Are temporary changes to rights of way needed while the site is worked</t>
+          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
@@ -6080,12 +6200,12 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>future-new-right-of-way</t>
+          <t>new-right-of-way</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Future new right of way</t>
+          <t>New right of way</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
@@ -6096,7 +6216,7 @@
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>Will new public rights of way be provided after extraction?</t>
+          <t>Will new public rights of way be provided within or adjacent to the site</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
@@ -6120,36 +6240,28 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>new-public-road</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>New public road</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Will new public roads be provided within the site</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -6159,53 +6271,37 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>Plans, drawings and supporting materials</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>plans-drawings-supporting-materials</t>
-        </is>
-      </c>
+      <c r="A117" s="2" t="n"/>
+      <c r="B117" s="2" t="n"/>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Additional materials and specifications that form part of the planning application</t>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>temp-right-of-way</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Temporary right of way changes</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr"/>
       <c r="I117" s="2" t="inlineStr"/>
       <c r="J117" s="2" t="inlineStr"/>
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Are temporary changes to rights of way needed while the site is worked</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -6219,17 +6315,17 @@
       <c r="B118" s="2" t="n"/>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Additional materials and specifications that form part of the planning application</t>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>inspection-address</t>
+          <t>future-new-right-of-way</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Inspection address</t>
+          <t>Future new right of way</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
@@ -6240,12 +6336,12 @@
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>Full postal address where supporting material can be inspected</t>
+          <t>Will new public rights of way be provided after extraction?</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -6255,45 +6351,45 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A119" s="2" t="n"/>
+      <c r="B119" s="2" t="n"/>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr"/>
-      <c r="G119" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H119" s="2" t="inlineStr"/>
       <c r="I119" s="2" t="inlineStr"/>
       <c r="J119" s="2" t="inlineStr"/>
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -6303,32 +6399,48 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n"/>
-      <c r="B120" s="2" t="n"/>
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Plans, drawings and supporting materials</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>plans-drawings-supporting-materials</t>
+        </is>
+      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Additional materials and specifications that form part of the planning application</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H120" s="2" t="inlineStr"/>
       <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
@@ -6338,7 +6450,7 @@
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6347,17 +6459,17 @@
       <c r="B121" s="2" t="n"/>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Additional materials and specifications that form part of the planning application</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>inspection-address</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Inspection address</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr"/>
@@ -6368,7 +6480,7 @@
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Full postal address where supporting material can be inspected</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
@@ -6378,13 +6490,21 @@
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n"/>
-      <c r="B122" s="2" t="n"/>
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -6392,12 +6512,12 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
@@ -6408,17 +6528,17 @@
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6432,12 +6552,12 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr"/>
@@ -6448,7 +6568,7 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
@@ -6463,53 +6583,37 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A124" s="2" t="n"/>
+      <c r="B124" s="2" t="n"/>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>site-boundary</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr"/>
       <c r="I124" s="2" t="inlineStr"/>
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -6523,41 +6627,33 @@
       <c r="B125" s="2" t="n"/>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>address-text</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Advice date</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr"/>
       <c r="I125" s="2" t="inlineStr"/>
       <c r="J125" s="2" t="inlineStr"/>
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -6571,36 +6667,28 @@
       <c r="B126" s="2" t="n"/>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr"/>
       <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
@@ -6615,8 +6703,16 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n"/>
-      <c r="B127" s="2" t="n"/>
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -6634,12 +6730,12 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>geometry</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr"/>
@@ -6648,17 +6744,17 @@
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6682,31 +6778,39 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr"/>
-      <c r="I128" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6730,26 +6834,34 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr"/>
-      <c r="I129" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J129" s="2" t="inlineStr"/>
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -6778,26 +6890,34 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr"/>
-      <c r="I130" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>uprns</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -6826,21 +6946,29 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr"/>
-      <c r="I131" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>usrns</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
@@ -6874,12 +7002,12 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr"/>
@@ -6888,12 +7016,12 @@
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -6903,39 +7031,31 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>Site ownership</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>site-ownership</t>
-        </is>
-      </c>
+      <c r="A133" s="2" t="n"/>
+      <c r="B133" s="2" t="n"/>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>site-owner</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Site owner</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>fullname</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr"/>
@@ -6944,17 +7064,17 @@
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6963,27 +7083,27 @@
       <c r="B134" s="2" t="n"/>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>site-owner</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Site owner</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr"/>
@@ -6992,17 +7112,17 @@
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7011,44 +7131,60 @@
       <c r="B135" s="2" t="n"/>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>applicant-interest</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr"/>
-      <c r="G135" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="H135" s="2" t="inlineStr"/>
       <c r="I135" s="2" t="inlineStr"/>
       <c r="J135" s="2" t="inlineStr"/>
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>Details of the applicant's interest in the land</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n"/>
-      <c r="B136" s="2" t="n"/>
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Site ownership</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>site-ownership</t>
+        </is>
+      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
@@ -7056,23 +7192,31 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>applicant-interest-adjoining-land</t>
+          <t>site-owner</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest adjoining land</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr"/>
-      <c r="G136" s="2" t="inlineStr"/>
+          <t>Site owner</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="H136" s="2" t="inlineStr"/>
       <c r="I136" s="2" t="inlineStr"/>
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>Description of the applicant's interest in the adjacent land</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
@@ -7087,45 +7231,45 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A137" s="2" t="n"/>
+      <c r="B137" s="2" t="n"/>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>site-owner</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr"/>
-      <c r="G137" s="2" t="inlineStr"/>
+          <t>Site owner</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="H137" s="2" t="inlineStr"/>
       <c r="I137" s="2" t="inlineStr"/>
       <c r="J137" s="2" t="inlineStr"/>
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -7139,17 +7283,17 @@
       <c r="B138" s="2" t="n"/>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>applicant-interest</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Applicant interest</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr"/>
@@ -7160,12 +7304,12 @@
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Details of the applicant's interest in the land</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -7179,17 +7323,17 @@
       <c r="B139" s="2" t="n"/>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>applicant-interest-adjoining-land</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Applicant interest adjoining land</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
@@ -7200,7 +7344,7 @@
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Description of the applicant's interest in the adjacent land</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
@@ -7210,13 +7354,21 @@
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n"/>
-      <c r="B140" s="2" t="n"/>
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -7224,36 +7376,28 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>fullname</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr"/>
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -7272,36 +7416,28 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr"/>
       <c r="H141" s="2" t="inlineStr"/>
       <c r="I141" s="2" t="inlineStr"/>
       <c r="J141" s="2" t="inlineStr"/>
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -7320,31 +7456,23 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr"/>
       <c r="I142" s="2" t="inlineStr"/>
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
@@ -7354,45 +7482,45 @@
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Storage facilities</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>storage-facilities</t>
-        </is>
-      </c>
+      <c r="A143" s="2" t="n"/>
+      <c r="B143" s="2" t="n"/>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>For oil and gas extraction developments, how chemicals will be stored</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>storage-facilities-description</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Storage facilities description</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr"/>
-      <c r="G143" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="H143" s="2" t="inlineStr"/>
       <c r="I143" s="2" t="inlineStr"/>
       <c r="J143" s="2" t="inlineStr"/>
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>Details and proposed facilities for the storage of oil, fuel and chemicals and the proposed means of their protection</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
@@ -7407,45 +7535,45 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>Trade effluent</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>trade-effluent</t>
-        </is>
-      </c>
+      <c r="A144" s="2" t="n"/>
+      <c r="B144" s="2" t="n"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>is-disposal-required</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Disposal required</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr"/>
-      <c r="G144" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="H144" s="2" t="inlineStr"/>
       <c r="I144" s="2" t="inlineStr"/>
       <c r="J144" s="2" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -7459,28 +7587,36 @@
       <c r="B145" s="2" t="n"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr"/>
-      <c r="G145" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H145" s="2" t="inlineStr"/>
       <c r="I145" s="2" t="inlineStr"/>
       <c r="J145" s="2" t="inlineStr"/>
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
@@ -7490,34 +7626,34 @@
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Trees and hedges information</t>
+          <t>Storage facilities</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>trees-hedges</t>
+          <t>storage-facilities</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+          <t>For oil and gas extraction developments, how chemicals will be stored</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>trees-on-site</t>
+          <t>storage-facilities-description</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Trees on site</t>
+          <t>Storage facilities description</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
@@ -7528,12 +7664,12 @@
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges are present on the proposed development site</t>
+          <t>Details and proposed facilities for the storage of oil, fuel and chemicals and the proposed means of their protection</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -7543,21 +7679,29 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n"/>
-      <c r="B147" s="2" t="n"/>
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Trade effluent</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>trade-effluent</t>
+        </is>
+      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>trees-on-adj-land</t>
+          <t>is-disposal-required</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Trees on adjacent land</t>
+          <t>Disposal required</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
@@ -7568,7 +7712,7 @@
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
+          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
@@ -7583,30 +7727,21 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Oil and gas permission types</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>oilgas-permission-type</t>
-        </is>
-      </c>
+      <c r="A148" s="2" t="n"/>
+      <c r="B148" s="2" t="n"/>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
-</t>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>oilgas-permission-types</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Oil and gas permission types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
@@ -7617,61 +7752,60 @@
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>List of permission types being applied for</t>
+          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n"/>
-      <c r="B149" s="2" t="n"/>
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>trees-hedges</t>
+        </is>
+      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
-</t>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>related-permissions</t>
+          <t>trees-on-site</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Related permissions[]</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Trees on site</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr"/>
       <c r="I149" s="2" t="inlineStr"/>
       <c r="J149" s="2" t="inlineStr"/>
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application that permission was received for</t>
+          <t>Whether trees or hedges are present on the proposed development site</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -7685,42 +7819,33 @@
       <c r="B150" s="2" t="n"/>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
-</t>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>related-permissions</t>
+          <t>trees-on-adj-land</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Related permissions[]</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>oilgas-permission-type</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>Oil and gas permission type</t>
-        </is>
-      </c>
+          <t>Trees on adjacent land</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr"/>
       <c r="I150" s="2" t="inlineStr"/>
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>An oil and gas related permission type</t>
+          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -7730,8 +7855,16 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n"/>
-      <c r="B151" s="2" t="n"/>
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Oil and gas permission types</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>oilgas-permission-type</t>
+        </is>
+      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
@@ -7740,36 +7873,28 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>related-permissions</t>
+          <t>oilgas-permission-types</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Related permissions[]</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>decision-date</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>Decision date</t>
-        </is>
-      </c>
+          <t>Oil and gas permission types[]</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr"/>
       <c r="I151" s="2" t="inlineStr"/>
       <c r="J151" s="2" t="inlineStr"/>
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>List of permission types being applied for</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -7799,12 +7924,12 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>condition-number</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Condition number</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr"/>
@@ -7813,7 +7938,7 @@
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>Number of any condition being breached</t>
+          <t>The reference for the related application that permission was received for</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
@@ -7823,7 +7948,7 @@
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7838,33 +7963,41 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>other-details</t>
+          <t>related-permissions</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Other details</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr"/>
-      <c r="G153" s="2" t="inlineStr"/>
+          <t>Related permissions[]</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>oilgas-permission-type</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>Oil and gas permission type</t>
+        </is>
+      </c>
       <c r="H153" s="2" t="inlineStr"/>
       <c r="I153" s="2" t="inlineStr"/>
       <c r="J153" s="2" t="inlineStr"/>
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>Explanation if other ground is selected</t>
+          <t>An oil and gas related permission type</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7879,28 +8012,36 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>will-consolidate-permissions</t>
+          <t>related-permissions</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Will consolidate permissions</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr"/>
-      <c r="G154" s="2" t="inlineStr"/>
+          <t>Related permissions[]</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>decision-date</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Decision date</t>
+        </is>
+      </c>
       <c r="H154" s="2" t="inlineStr"/>
       <c r="I154" s="2" t="inlineStr"/>
       <c r="J154" s="2" t="inlineStr"/>
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant looking to consolidate permissions?</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -7920,23 +8061,31 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>details</t>
+          <t>related-permissions</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr"/>
-      <c r="G155" s="2" t="inlineStr"/>
+          <t>Related permissions[]</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>condition-number</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Condition number</t>
+        </is>
+      </c>
       <c r="H155" s="2" t="inlineStr"/>
       <c r="I155" s="2" t="inlineStr"/>
       <c r="J155" s="2" t="inlineStr"/>
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>Details about the consolidation or update of permissions</t>
+          <t>Number of any condition being breached</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
@@ -7961,31 +8110,23 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>related-proposals</t>
+          <t>other-details</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Related proposals[]</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Other details</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr"/>
       <c r="I156" s="2" t="inlineStr"/>
       <c r="J156" s="2" t="inlineStr"/>
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>Explanation if other ground is selected</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
@@ -7995,7 +8136,7 @@
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8010,36 +8151,28 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>related-proposals</t>
+          <t>will-consolidate-permissions</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Related proposals[]</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t>application-type</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>Application type</t>
-        </is>
-      </c>
+          <t>Will consolidate permissions</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr"/>
       <c r="I157" s="2" t="inlineStr"/>
       <c r="J157" s="2" t="inlineStr"/>
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>The type of planning application</t>
+          <t>Is the applicant looking to consolidate permissions?</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -8059,84 +8192,77 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>related-proposals</t>
+          <t>details</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Related proposals[]</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>decision-date</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>Decision date</t>
-        </is>
-      </c>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr"/>
       <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>Details about the consolidation or update of permissions</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>Development type</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>dev-type</t>
-        </is>
-      </c>
+      <c r="A159" s="2" t="n"/>
+      <c r="B159" s="2" t="n"/>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
+          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
+</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>development-phase</t>
+          <t>related-proposals</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Development phase</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr"/>
-      <c r="G159" s="2" t="inlineStr"/>
+          <t>Related proposals[]</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H159" s="2" t="inlineStr"/>
       <c r="I159" s="2" t="inlineStr"/>
       <c r="J159" s="2" t="inlineStr"/>
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>Phases of oil and gas development the application covers</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -8150,33 +8276,42 @@
       <c r="B160" s="2" t="n"/>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
+          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
+</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>related-proposals</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Development description</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr"/>
-      <c r="G160" s="2" t="inlineStr"/>
+          <t>Related proposals[]</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>application-type</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Application type</t>
+        </is>
+      </c>
       <c r="H160" s="2" t="inlineStr"/>
       <c r="I160" s="2" t="inlineStr"/>
       <c r="J160" s="2" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>Brief description of the development, including main oils, gases, and machinery</t>
+          <t>The type of planning application</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -8190,33 +8325,42 @@
       <c r="B161" s="2" t="n"/>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
+          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
+</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>quantity-cubic-metres</t>
+          <t>related-proposals</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Quantity cubic metres</t>
-        </is>
-      </c>
-      <c r="F161" s="2" t="inlineStr"/>
-      <c r="G161" s="2" t="inlineStr"/>
+          <t>Related proposals[]</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>decision-date</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>Decision date</t>
+        </is>
+      </c>
       <c r="H161" s="2" t="inlineStr"/>
       <c r="I161" s="2" t="inlineStr"/>
       <c r="J161" s="2" t="inlineStr"/>
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>Quantity of oil or gas involved in cubic metres</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -8226,8 +8370,16 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n"/>
-      <c r="B162" s="2" t="n"/>
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Development type</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>dev-type</t>
+        </is>
+      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
@@ -8235,12 +8387,12 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>permission-period-years</t>
+          <t>development-phase</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Permission period years</t>
+          <t>Development phase</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
@@ -8251,17 +8403,17 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>Period of permission sought in years</t>
+          <t>Phases of oil and gas development the application covers</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8275,12 +8427,12 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>hydrocarbon-licence-block</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Hydrocarbon licence block</t>
+          <t>Development description</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr"/>
@@ -8291,7 +8443,7 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>Hydrocarbon licence block where the development is located</t>
+          <t>Brief description of the development, including main oils, gases, and machinery</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
@@ -8315,12 +8467,12 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>surface-site-area-hectares</t>
+          <t>quantity-cubic-metres</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Surface site area hectares</t>
+          <t>Quantity cubic metres</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr"/>
@@ -8331,7 +8483,7 @@
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>Surface site area in hectares</t>
+          <t>Quantity of oil or gas involved in cubic metres</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
@@ -8341,7 +8493,7 @@
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8507,12 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>site-hectares-provided-by</t>
+          <t>permission-period-years</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Site hectares provided by</t>
+          <t>Permission period years</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr"/>
@@ -8371,12 +8523,12 @@
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site hectares value (applicant or system)</t>
+          <t>Period of permission sought in years</t>
         </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -8395,12 +8547,12 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>environmental-statement</t>
+          <t>hydrocarbon-licence-block</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Environmental statement</t>
+          <t>Hydrocarbon licence block</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr"/>
@@ -8411,12 +8563,12 @@
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>Is an Environmental Statement attached to the application</t>
+          <t>Hydrocarbon licence block where the development is located</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -8435,12 +8587,12 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>environmental-statement-reference</t>
+          <t>surface-site-area-hectares</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Environmental statement reference</t>
+          <t>Surface site area hectares</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr"/>
@@ -8451,12 +8603,12 @@
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>Reference to the environmental statement document</t>
+          <t>Surface site area in hectares</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -8466,29 +8618,21 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>Voluntary agreement</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>vol-agreement</t>
-        </is>
-      </c>
+      <c r="A168" s="2" t="n"/>
+      <c r="B168" s="2" t="n"/>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Details of any voluntary agreements made as part of an oil and gas extraction application.</t>
+          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>draft-agreement-included</t>
+          <t>site-hectares-provided-by</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Draft agreement included</t>
+          <t>Site hectares provided by</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr"/>
@@ -8499,17 +8643,17 @@
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>Has an outline or draft agreement been included? (True / False)</t>
+          <t>Who provided the site hectares value (applicant or system)</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8518,17 +8662,17 @@
       <c r="B169" s="2" t="n"/>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Details of any voluntary agreements made as part of an oil and gas extraction application.</t>
+          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>agreement-summary</t>
+          <t>environmental-statement</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Agreement summary</t>
+          <t>Environmental statement</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr"/>
@@ -8539,15 +8683,143 @@
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr">
         <is>
+          <t>Is an Environmental Statement attached to the application</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n"/>
+      <c r="B170" s="2" t="n"/>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>environmental-statement-reference</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Environmental statement reference</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr"/>
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr"/>
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>Reference to the environmental statement document</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Voluntary agreement</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>vol-agreement</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Details of any voluntary agreements made as part of an oil and gas extraction application.</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>draft-agreement-included</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Draft agreement included</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr"/>
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr"/>
+      <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>Has an outline or draft agreement been included? (True / False)</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n"/>
+      <c r="B172" s="2" t="n"/>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Details of any voluntary agreements made as part of an oil and gas extraction application.</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>agreement-summary</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Agreement summary</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr"/>
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
           <t>Summary of the agreement</t>
         </is>
       </c>
-      <c r="M169" s="2" t="inlineStr">
+      <c r="M172" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N169" s="2" t="inlineStr">
+      <c r="N172" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -8555,66 +8827,66 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="B119:B123"/>
-    <mergeCell ref="B51:B54"/>
-    <mergeCell ref="B143"/>
-    <mergeCell ref="B148:B158"/>
-    <mergeCell ref="B55"/>
-    <mergeCell ref="A124:A132"/>
+    <mergeCell ref="A162:A170"/>
+    <mergeCell ref="B149:B150"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="B68"/>
+    <mergeCell ref="A149:A150"/>
+    <mergeCell ref="A37:A43"/>
+    <mergeCell ref="B94:B112"/>
+    <mergeCell ref="A113:A119"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A60:A65"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="A67:A76"/>
-    <mergeCell ref="A137:A142"/>
-    <mergeCell ref="B117:B118"/>
-    <mergeCell ref="A143"/>
-    <mergeCell ref="A159:A167"/>
-    <mergeCell ref="B92:B109"/>
-    <mergeCell ref="A59"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B42:B47"/>
-    <mergeCell ref="A77:A81"/>
-    <mergeCell ref="B124:B132"/>
-    <mergeCell ref="B59"/>
-    <mergeCell ref="A133:A136"/>
-    <mergeCell ref="B66"/>
-    <mergeCell ref="A84:A91"/>
-    <mergeCell ref="B110:B116"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="B67:B76"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B60:B65"/>
-    <mergeCell ref="A92:A109"/>
-    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="A68"/>
+    <mergeCell ref="B37:B43"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="A151:A161"/>
+    <mergeCell ref="B140:B145"/>
+    <mergeCell ref="B62:B67"/>
+    <mergeCell ref="B136:B139"/>
+    <mergeCell ref="B162:B170"/>
+    <mergeCell ref="A122:A126"/>
+    <mergeCell ref="B151:B161"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="B127:B135"/>
+    <mergeCell ref="B86:B93"/>
+    <mergeCell ref="A94:A112"/>
+    <mergeCell ref="A69:A78"/>
+    <mergeCell ref="B24:B32"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="A147:A148"/>
+    <mergeCell ref="A61"/>
+    <mergeCell ref="B53:B56"/>
+    <mergeCell ref="A136:A139"/>
+    <mergeCell ref="B171:B172"/>
+    <mergeCell ref="B147:B148"/>
+    <mergeCell ref="B113:B119"/>
+    <mergeCell ref="A146"/>
+    <mergeCell ref="B44:B49"/>
+    <mergeCell ref="B122:B126"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="A127:A135"/>
+    <mergeCell ref="A86:A93"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B168:B169"/>
-    <mergeCell ref="B137:B142"/>
-    <mergeCell ref="A66"/>
-    <mergeCell ref="B133:B136"/>
-    <mergeCell ref="B84:B91"/>
-    <mergeCell ref="A110:A116"/>
-    <mergeCell ref="A119:A123"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="A42:A47"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B77:B81"/>
-    <mergeCell ref="A148:A158"/>
-    <mergeCell ref="A55"/>
+    <mergeCell ref="A53:A56"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="B69:B78"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61"/>
+    <mergeCell ref="B57"/>
+    <mergeCell ref="A171:A172"/>
+    <mergeCell ref="A24:A32"/>
+    <mergeCell ref="A140:A145"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B159:B167"/>
-    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="A57"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="A44:A49"/>
+    <mergeCell ref="B146"/>
+    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
